--- a/Docs/KMS_MA-9_Pinout.xlsx
+++ b/Docs/KMS_MA-9_Pinout.xlsx
@@ -2,18 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rik\Documents\CAD\SuperMX-5\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F28205D-13FE-4830-98A6-A9394C073AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66BAA61-BFD7-4148-B4EA-C239665842C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{48E6C7CE-85E9-4645-82F2-16F1ED18B360}"/>
+    <workbookView xWindow="15120" yWindow="0" windowWidth="23385" windowHeight="20985" activeTab="3" xr2:uid="{48E6C7CE-85E9-4645-82F2-16F1ED18B360}"/>
   </bookViews>
   <sheets>
-    <sheet name="Blad1" sheetId="1" r:id="rId1"/>
+    <sheet name="1-KMS_MA9" sheetId="3" r:id="rId1"/>
+    <sheet name="2-PDM32" sheetId="2" r:id="rId2"/>
+    <sheet name="3-DeltaABS" sheetId="4" r:id="rId3"/>
+    <sheet name="4-RaceTCS" sheetId="5" r:id="rId4"/>
+    <sheet name="1-KMS(OLD)" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="586">
   <si>
     <t>MA-9 ECU Pinout</t>
   </si>
@@ -543,6 +547,1257 @@
   </si>
   <si>
     <t>Purple/Black</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>High Power Output 1</t>
+  </si>
+  <si>
+    <t>High Power Output 2</t>
+  </si>
+  <si>
+    <t>High Power Output 3</t>
+  </si>
+  <si>
+    <t>High Power Output 4</t>
+  </si>
+  <si>
+    <t>Mid Power Output 1</t>
+  </si>
+  <si>
+    <t>Mid Power Output 2</t>
+  </si>
+  <si>
+    <t>Mid Power Output 3</t>
+  </si>
+  <si>
+    <t>Mid Power Output 4</t>
+  </si>
+  <si>
+    <t>Mid Power Output 5</t>
+  </si>
+  <si>
+    <t>Mid Power Output 6</t>
+  </si>
+  <si>
+    <t>Mid Power Output 7</t>
+  </si>
+  <si>
+    <t>Mid Power Output 8</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>CAN AIM Low</t>
+  </si>
+  <si>
+    <t>Low Power Output 1</t>
+  </si>
+  <si>
+    <t>Low Power Output 2</t>
+  </si>
+  <si>
+    <t>Low Power Output 3</t>
+  </si>
+  <si>
+    <t>Low Power Output 4</t>
+  </si>
+  <si>
+    <t>Low Power Output 5</t>
+  </si>
+  <si>
+    <t>Low Power Output 6</t>
+  </si>
+  <si>
+    <t>Low Power Output 7</t>
+  </si>
+  <si>
+    <t>Low Power Output 8</t>
+  </si>
+  <si>
+    <t>CAN AIM High</t>
+  </si>
+  <si>
+    <t>Channel Input 11</t>
+  </si>
+  <si>
+    <t>Channel Input 12</t>
+  </si>
+  <si>
+    <t>CAN2 High</t>
+  </si>
+  <si>
+    <t>CAN2 Low</t>
+  </si>
+  <si>
+    <t>CAN ECU LOW/RS232RX</t>
+  </si>
+  <si>
+    <t>CAN ECU High/RS232TX</t>
+  </si>
+  <si>
+    <t>+Vb ext CAN</t>
+  </si>
+  <si>
+    <t>+Vb Out CAN</t>
+  </si>
+  <si>
+    <t>Pin #</t>
+  </si>
+  <si>
+    <t>Pin ID</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>Connector: 1</t>
+  </si>
+  <si>
+    <t>35 Pins AMP Connector (Black Connector)</t>
+  </si>
+  <si>
+    <t>2-1-1</t>
+  </si>
+  <si>
+    <t>2-2-2</t>
+  </si>
+  <si>
+    <t>2-3-3</t>
+  </si>
+  <si>
+    <t>2-5-5</t>
+  </si>
+  <si>
+    <t>2-1-2</t>
+  </si>
+  <si>
+    <t>2-2-3</t>
+  </si>
+  <si>
+    <t>2-3-4</t>
+  </si>
+  <si>
+    <t>2-2-12</t>
+  </si>
+  <si>
+    <t>2-1-13</t>
+  </si>
+  <si>
+    <t>2-1-14</t>
+  </si>
+  <si>
+    <t>2-2-15</t>
+  </si>
+  <si>
+    <t>2-2-23</t>
+  </si>
+  <si>
+    <t>2-1-3</t>
+  </si>
+  <si>
+    <t>2-1-4</t>
+  </si>
+  <si>
+    <t>2-1-5</t>
+  </si>
+  <si>
+    <t>2-1-6</t>
+  </si>
+  <si>
+    <t>2-1-7</t>
+  </si>
+  <si>
+    <t>2-1-8</t>
+  </si>
+  <si>
+    <t>2-1-9</t>
+  </si>
+  <si>
+    <t>2-1-10</t>
+  </si>
+  <si>
+    <t>2-1-11</t>
+  </si>
+  <si>
+    <t>2-1-12</t>
+  </si>
+  <si>
+    <t>2-1-15</t>
+  </si>
+  <si>
+    <t>2-1-16</t>
+  </si>
+  <si>
+    <t>2-1-17</t>
+  </si>
+  <si>
+    <t>2-1-18</t>
+  </si>
+  <si>
+    <t>2-1-19</t>
+  </si>
+  <si>
+    <t>2-1-20</t>
+  </si>
+  <si>
+    <t>2-1-21</t>
+  </si>
+  <si>
+    <t>2-1-22</t>
+  </si>
+  <si>
+    <t>2-1-23</t>
+  </si>
+  <si>
+    <t>2-1-24</t>
+  </si>
+  <si>
+    <t>2-1-25</t>
+  </si>
+  <si>
+    <t>2-1-26</t>
+  </si>
+  <si>
+    <t>2-1-27</t>
+  </si>
+  <si>
+    <t>2-1-28</t>
+  </si>
+  <si>
+    <t>2-1-29</t>
+  </si>
+  <si>
+    <t>2-1-30</t>
+  </si>
+  <si>
+    <t>2-1-31</t>
+  </si>
+  <si>
+    <t>2-1-32</t>
+  </si>
+  <si>
+    <t>2-1-33</t>
+  </si>
+  <si>
+    <t>2-1-34</t>
+  </si>
+  <si>
+    <t>2-1-35</t>
+  </si>
+  <si>
+    <t>35 Pins AMP Connector (Grey Connector)</t>
+  </si>
+  <si>
+    <t>Connector: 2</t>
+  </si>
+  <si>
+    <t>Hald Bridge Power Output 1</t>
+  </si>
+  <si>
+    <t>Hald Bridge Power Output 2</t>
+  </si>
+  <si>
+    <t>Low Power Output 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid Power Output 9 </t>
+  </si>
+  <si>
+    <t>Mid Power Output 10</t>
+  </si>
+  <si>
+    <t>Low Power Output 10</t>
+  </si>
+  <si>
+    <t>Low Power Output 11</t>
+  </si>
+  <si>
+    <t>Mid Power Output 11</t>
+  </si>
+  <si>
+    <t>Mid Power Output 12</t>
+  </si>
+  <si>
+    <t>Low Power Output 12</t>
+  </si>
+  <si>
+    <t>P GND</t>
+  </si>
+  <si>
+    <t>LIN</t>
+  </si>
+  <si>
+    <t>+5V Analog Vreference</t>
+  </si>
+  <si>
+    <t>+Vb Output</t>
+  </si>
+  <si>
+    <t>Speed 2 Input</t>
+  </si>
+  <si>
+    <t>Speed 1 Input</t>
+  </si>
+  <si>
+    <t>Channel Input 9</t>
+  </si>
+  <si>
+    <t>Channel Input 10</t>
+  </si>
+  <si>
+    <t>Ignition</t>
+  </si>
+  <si>
+    <t>Half Bridge Power Output 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Channel Input 1 </t>
+  </si>
+  <si>
+    <t>Channel Input 2</t>
+  </si>
+  <si>
+    <t>Channel Input 3</t>
+  </si>
+  <si>
+    <t>Channel Input 4</t>
+  </si>
+  <si>
+    <t>Channel Input 5</t>
+  </si>
+  <si>
+    <t>Channel Input 6</t>
+  </si>
+  <si>
+    <t>Channel Input 7</t>
+  </si>
+  <si>
+    <t>Channel Input 8</t>
+  </si>
+  <si>
+    <t>Half Bridge Power Output 4</t>
+  </si>
+  <si>
+    <t>2-2-1</t>
+  </si>
+  <si>
+    <t>2-2-4</t>
+  </si>
+  <si>
+    <t>2-2-5</t>
+  </si>
+  <si>
+    <t>2-2-6</t>
+  </si>
+  <si>
+    <t>2-2-7</t>
+  </si>
+  <si>
+    <t>2-2-8</t>
+  </si>
+  <si>
+    <t>2-2-9</t>
+  </si>
+  <si>
+    <t>2-2-10</t>
+  </si>
+  <si>
+    <t>2-2-11</t>
+  </si>
+  <si>
+    <t>2-2-13</t>
+  </si>
+  <si>
+    <t>2-2-14</t>
+  </si>
+  <si>
+    <t>2-2-16</t>
+  </si>
+  <si>
+    <t>2-2-17</t>
+  </si>
+  <si>
+    <t>2-2-18</t>
+  </si>
+  <si>
+    <t>2-2-19</t>
+  </si>
+  <si>
+    <t>2-2-20</t>
+  </si>
+  <si>
+    <t>2-2-21</t>
+  </si>
+  <si>
+    <t>2-2-22</t>
+  </si>
+  <si>
+    <t>2-2-24</t>
+  </si>
+  <si>
+    <t>2-2-25</t>
+  </si>
+  <si>
+    <t>2-2-26</t>
+  </si>
+  <si>
+    <t>2-2-27</t>
+  </si>
+  <si>
+    <t>2-2-28</t>
+  </si>
+  <si>
+    <t>2-2-29</t>
+  </si>
+  <si>
+    <t>2-2-30</t>
+  </si>
+  <si>
+    <t>2-2-31</t>
+  </si>
+  <si>
+    <t>2-2-32</t>
+  </si>
+  <si>
+    <t>2-2-33</t>
+  </si>
+  <si>
+    <t>2-2-34</t>
+  </si>
+  <si>
+    <t>2-2-35</t>
+  </si>
+  <si>
+    <t>LVDS Link</t>
+  </si>
+  <si>
+    <t>Connector: 3</t>
+  </si>
+  <si>
+    <t>Serial Data</t>
+  </si>
+  <si>
+    <t>+V Power</t>
+  </si>
+  <si>
+    <t>Serial Data+</t>
+  </si>
+  <si>
+    <t>2-3-1</t>
+  </si>
+  <si>
+    <t>2-3-2</t>
+  </si>
+  <si>
+    <t>Connector: 4</t>
+  </si>
+  <si>
+    <t>USB</t>
+  </si>
+  <si>
+    <t>USB D+</t>
+  </si>
+  <si>
+    <t>USB D-</t>
+  </si>
+  <si>
+    <t>2-4-1</t>
+  </si>
+  <si>
+    <t>2-4-2</t>
+  </si>
+  <si>
+    <t>2-4-3</t>
+  </si>
+  <si>
+    <t>Connector: 5</t>
+  </si>
+  <si>
+    <t>Video Input</t>
+  </si>
+  <si>
+    <t>Video Input 1</t>
+  </si>
+  <si>
+    <t>Video Input 2</t>
+  </si>
+  <si>
+    <t>+Vb Output CAM</t>
+  </si>
+  <si>
+    <t>Connector: 6</t>
+  </si>
+  <si>
+    <t>120A Ampenol Surlock</t>
+  </si>
+  <si>
+    <t>+9-15Vdc (From Battery)</t>
+  </si>
+  <si>
+    <t>2-5-1</t>
+  </si>
+  <si>
+    <t>2-5-2</t>
+  </si>
+  <si>
+    <t>2-5-3</t>
+  </si>
+  <si>
+    <t>2-5-4</t>
+  </si>
+  <si>
+    <t>2-6-1</t>
+  </si>
+  <si>
+    <t>34 Pins AMP Connector A</t>
+  </si>
+  <si>
+    <t>26 Pins AMP Connector B</t>
+  </si>
+  <si>
+    <t>34 Pins AMP Connector C</t>
+  </si>
+  <si>
+    <t>1-1-1</t>
+  </si>
+  <si>
+    <t>1-1-2</t>
+  </si>
+  <si>
+    <t>1-1-3</t>
+  </si>
+  <si>
+    <t>1-1-4</t>
+  </si>
+  <si>
+    <t>1-1-5</t>
+  </si>
+  <si>
+    <t>1-1-6</t>
+  </si>
+  <si>
+    <t>1-1-7</t>
+  </si>
+  <si>
+    <t>1-1-8</t>
+  </si>
+  <si>
+    <t>1-1-9</t>
+  </si>
+  <si>
+    <t>1-1-10</t>
+  </si>
+  <si>
+    <t>1-1-11</t>
+  </si>
+  <si>
+    <t>1-1-12</t>
+  </si>
+  <si>
+    <t>1-1-13</t>
+  </si>
+  <si>
+    <t>1-1-14</t>
+  </si>
+  <si>
+    <t>1-1-15</t>
+  </si>
+  <si>
+    <t>1-1-16</t>
+  </si>
+  <si>
+    <t>1-1-17</t>
+  </si>
+  <si>
+    <t>1-1-18</t>
+  </si>
+  <si>
+    <t>1-1-19</t>
+  </si>
+  <si>
+    <t>1-1-20</t>
+  </si>
+  <si>
+    <t>1-1-21</t>
+  </si>
+  <si>
+    <t>1-1-22</t>
+  </si>
+  <si>
+    <t>1-1-23</t>
+  </si>
+  <si>
+    <t>1-1-24</t>
+  </si>
+  <si>
+    <t>1-1-25</t>
+  </si>
+  <si>
+    <t>1-1-26</t>
+  </si>
+  <si>
+    <t>1-1-27</t>
+  </si>
+  <si>
+    <t>1-1-28</t>
+  </si>
+  <si>
+    <t>1-1-29</t>
+  </si>
+  <si>
+    <t>1-1-30</t>
+  </si>
+  <si>
+    <t>1-1-31</t>
+  </si>
+  <si>
+    <t>1-1-32</t>
+  </si>
+  <si>
+    <t>1-1-33</t>
+  </si>
+  <si>
+    <t>1-1-34</t>
+  </si>
+  <si>
+    <t>1-2-1</t>
+  </si>
+  <si>
+    <t>1-2-2</t>
+  </si>
+  <si>
+    <t>1-2-3</t>
+  </si>
+  <si>
+    <t>1-2-4</t>
+  </si>
+  <si>
+    <t>1-2-5</t>
+  </si>
+  <si>
+    <t>1-2-6</t>
+  </si>
+  <si>
+    <t>1-2-7</t>
+  </si>
+  <si>
+    <t>1-2-8</t>
+  </si>
+  <si>
+    <t>1-2-9</t>
+  </si>
+  <si>
+    <t>1-2-10</t>
+  </si>
+  <si>
+    <t>1-2-11</t>
+  </si>
+  <si>
+    <t>1-2-12</t>
+  </si>
+  <si>
+    <t>1-2-13</t>
+  </si>
+  <si>
+    <t>1-2-14</t>
+  </si>
+  <si>
+    <t>1-2-15</t>
+  </si>
+  <si>
+    <t>1-2-16</t>
+  </si>
+  <si>
+    <t>1-2-17</t>
+  </si>
+  <si>
+    <t>1-2-18</t>
+  </si>
+  <si>
+    <t>1-2-19</t>
+  </si>
+  <si>
+    <t>1-2-20</t>
+  </si>
+  <si>
+    <t>1-2-21</t>
+  </si>
+  <si>
+    <t>1-2-22</t>
+  </si>
+  <si>
+    <t>1-2-23</t>
+  </si>
+  <si>
+    <t>1-2-24</t>
+  </si>
+  <si>
+    <t>1-2-25</t>
+  </si>
+  <si>
+    <t>1-2-26</t>
+  </si>
+  <si>
+    <t>1-3-2</t>
+  </si>
+  <si>
+    <t>1-3-1</t>
+  </si>
+  <si>
+    <t>1-3-3</t>
+  </si>
+  <si>
+    <t>1-3-4</t>
+  </si>
+  <si>
+    <t>1-3-5</t>
+  </si>
+  <si>
+    <t>1-3-6</t>
+  </si>
+  <si>
+    <t>1-3-7</t>
+  </si>
+  <si>
+    <t>1-3-8</t>
+  </si>
+  <si>
+    <t>1-3-9</t>
+  </si>
+  <si>
+    <t>1-3-10</t>
+  </si>
+  <si>
+    <t>1-3-11</t>
+  </si>
+  <si>
+    <t>1-3-12</t>
+  </si>
+  <si>
+    <t>1-3-13</t>
+  </si>
+  <si>
+    <t>1-3-14</t>
+  </si>
+  <si>
+    <t>1-3-15</t>
+  </si>
+  <si>
+    <t>1-3-16</t>
+  </si>
+  <si>
+    <t>1-3-17</t>
+  </si>
+  <si>
+    <t>1-3-18</t>
+  </si>
+  <si>
+    <t>1-3-19</t>
+  </si>
+  <si>
+    <t>1-3-20</t>
+  </si>
+  <si>
+    <t>1-3-21</t>
+  </si>
+  <si>
+    <t>1-3-22</t>
+  </si>
+  <si>
+    <t>1-3-23</t>
+  </si>
+  <si>
+    <t>1-3-24</t>
+  </si>
+  <si>
+    <t>1-3-25</t>
+  </si>
+  <si>
+    <t>1-3-26</t>
+  </si>
+  <si>
+    <t>1-3-27</t>
+  </si>
+  <si>
+    <t>1-3-28</t>
+  </si>
+  <si>
+    <t>1-3-29</t>
+  </si>
+  <si>
+    <t>1-3-30</t>
+  </si>
+  <si>
+    <t>1-3-31</t>
+  </si>
+  <si>
+    <t>1-3-32</t>
+  </si>
+  <si>
+    <t>1-3-33</t>
+  </si>
+  <si>
+    <t>1-3-34</t>
+  </si>
+  <si>
+    <t>Interface Connector DTM06-12S</t>
+  </si>
+  <si>
+    <t>Power Ground</t>
+  </si>
+  <si>
+    <t>CAN Low</t>
+  </si>
+  <si>
+    <t>CAN High</t>
+  </si>
+  <si>
+    <t>ABS Active Output</t>
+  </si>
+  <si>
+    <t>Brake Light Output</t>
+  </si>
+  <si>
+    <t>Speedometer Output</t>
+  </si>
+  <si>
+    <t>Front Right Wheel Speed Output</t>
+  </si>
+  <si>
+    <t>Front Left Wheel Speed Output</t>
+  </si>
+  <si>
+    <t>Rear Left Wheel Speed Output</t>
+  </si>
+  <si>
+    <t>Rear Right Wheel Speed Output</t>
+  </si>
+  <si>
+    <t>Not Used</t>
+  </si>
+  <si>
+    <t>+15 Ignition 12V Feed</t>
+  </si>
+  <si>
+    <t>3-1-1</t>
+  </si>
+  <si>
+    <t>3-1-2</t>
+  </si>
+  <si>
+    <t>3-1-3</t>
+  </si>
+  <si>
+    <t>3-1-4</t>
+  </si>
+  <si>
+    <t>3-1-5</t>
+  </si>
+  <si>
+    <t>3-1-6</t>
+  </si>
+  <si>
+    <t>3-1-7</t>
+  </si>
+  <si>
+    <t>3-1-8</t>
+  </si>
+  <si>
+    <t>3-1-9</t>
+  </si>
+  <si>
+    <t>3-1-10</t>
+  </si>
+  <si>
+    <t>3-1-11</t>
+  </si>
+  <si>
+    <t>3-1-12</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t>1C</t>
+  </si>
+  <si>
+    <t>1D</t>
+  </si>
+  <si>
+    <t>1E</t>
+  </si>
+  <si>
+    <t>1F</t>
+  </si>
+  <si>
+    <t>1G</t>
+  </si>
+  <si>
+    <t>1H</t>
+  </si>
+  <si>
+    <t>1J</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>1L</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>2A</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>2C</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>2E</t>
+  </si>
+  <si>
+    <t>2F</t>
+  </si>
+  <si>
+    <t>2G</t>
+  </si>
+  <si>
+    <t>2H</t>
+  </si>
+  <si>
+    <t>2J</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>2L</t>
+  </si>
+  <si>
+    <t>2M</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>3C</t>
+  </si>
+  <si>
+    <t>3D</t>
+  </si>
+  <si>
+    <t>3E</t>
+  </si>
+  <si>
+    <t>3F</t>
+  </si>
+  <si>
+    <t>3G</t>
+  </si>
+  <si>
+    <t>3H</t>
+  </si>
+  <si>
+    <t>3J</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>3L</t>
+  </si>
+  <si>
+    <t>3M</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>4C</t>
+  </si>
+  <si>
+    <t>4D</t>
+  </si>
+  <si>
+    <t>4E</t>
+  </si>
+  <si>
+    <t>4F</t>
+  </si>
+  <si>
+    <t>4G</t>
+  </si>
+  <si>
+    <t>4H</t>
+  </si>
+  <si>
+    <t>4J</t>
+  </si>
+  <si>
+    <t>4K</t>
+  </si>
+  <si>
+    <t>4L</t>
+  </si>
+  <si>
+    <t>4M</t>
+  </si>
+  <si>
+    <t>Inj/Coil Output 8</t>
+  </si>
+  <si>
+    <t>Inj/Coil Output 7</t>
+  </si>
+  <si>
+    <t>Inj/Coil Output 6</t>
+  </si>
+  <si>
+    <t>Inj/Coil Output 5</t>
+  </si>
+  <si>
+    <t>Inj/Coil Output 4</t>
+  </si>
+  <si>
+    <t>Inj/Coil Output 3</t>
+  </si>
+  <si>
+    <t>Inj/Coil Output 2</t>
+  </si>
+  <si>
+    <t>Inj/Coil Output 1</t>
+  </si>
+  <si>
+    <t>(PWR)</t>
+  </si>
+  <si>
+    <t>Inj/Coil Input 8</t>
+  </si>
+  <si>
+    <t>Inj/Coil Input 7</t>
+  </si>
+  <si>
+    <t>Inj/Coil Input 6</t>
+  </si>
+  <si>
+    <t>Inj/Coil Input 5</t>
+  </si>
+  <si>
+    <t>Inj/Coil Input 4</t>
+  </si>
+  <si>
+    <t>Inj/Coil Input 3</t>
+  </si>
+  <si>
+    <t>Inj/Coil Input 2</t>
+  </si>
+  <si>
+    <t>Inj/Coil Input 1</t>
+  </si>
+  <si>
+    <t>Pot In</t>
+  </si>
+  <si>
+    <t>D-</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>Vbus</t>
+  </si>
+  <si>
+    <t>Wheel In FR</t>
+  </si>
+  <si>
+    <t>Wheel In FL</t>
+  </si>
+  <si>
+    <t>Wheel In RL</t>
+  </si>
+  <si>
+    <t>Wheel In RR</t>
+  </si>
+  <si>
+    <t>+V5</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
+    <t>Clutch In</t>
+  </si>
+  <si>
+    <t>Led Out</t>
+  </si>
+  <si>
+    <t>0-5V Out</t>
+  </si>
+  <si>
+    <t>+12 Ignition</t>
+  </si>
+  <si>
+    <t>4-1-1A</t>
+  </si>
+  <si>
+    <t>4-1-1B</t>
+  </si>
+  <si>
+    <t>4-1-1C</t>
+  </si>
+  <si>
+    <t>4-1-1D</t>
+  </si>
+  <si>
+    <t>4-1-1E</t>
+  </si>
+  <si>
+    <t>4-1-1F</t>
+  </si>
+  <si>
+    <t>4-1-1G</t>
+  </si>
+  <si>
+    <t>4-1-1H</t>
+  </si>
+  <si>
+    <t>4-1-1J</t>
+  </si>
+  <si>
+    <t>4-1-1K</t>
+  </si>
+  <si>
+    <t>4-1-1L</t>
+  </si>
+  <si>
+    <t>4-1-1M</t>
+  </si>
+  <si>
+    <t>4-1-2A</t>
+  </si>
+  <si>
+    <t>4-1-2B</t>
+  </si>
+  <si>
+    <t>4-1-2C</t>
+  </si>
+  <si>
+    <t>4-1-2D</t>
+  </si>
+  <si>
+    <t>4-1-2E</t>
+  </si>
+  <si>
+    <t>4-1-2F</t>
+  </si>
+  <si>
+    <t>4-1-2G</t>
+  </si>
+  <si>
+    <t>4-1-2H</t>
+  </si>
+  <si>
+    <t>4-1-2J</t>
+  </si>
+  <si>
+    <t>4-1-2K</t>
+  </si>
+  <si>
+    <t>4-1-2L</t>
+  </si>
+  <si>
+    <t>4-1-2M</t>
+  </si>
+  <si>
+    <t>4-1-3A</t>
+  </si>
+  <si>
+    <t>4-1-3B</t>
+  </si>
+  <si>
+    <t>4-1-3C</t>
+  </si>
+  <si>
+    <t>4-1-3D</t>
+  </si>
+  <si>
+    <t>4-1-3E</t>
+  </si>
+  <si>
+    <t>4-1-3F</t>
+  </si>
+  <si>
+    <t>4-1-3G</t>
+  </si>
+  <si>
+    <t>4-1-3H</t>
+  </si>
+  <si>
+    <t>4-1-3J</t>
+  </si>
+  <si>
+    <t>4-1-3K</t>
+  </si>
+  <si>
+    <t>4-1-3L</t>
+  </si>
+  <si>
+    <t>4-1-3M</t>
+  </si>
+  <si>
+    <t>4-1-4A</t>
+  </si>
+  <si>
+    <t>4-1-4B</t>
+  </si>
+  <si>
+    <t>4-1-4C</t>
+  </si>
+  <si>
+    <t>4-1-4D</t>
+  </si>
+  <si>
+    <t>4-1-4E</t>
+  </si>
+  <si>
+    <t>4-1-4F</t>
+  </si>
+  <si>
+    <t>4-1-4G</t>
+  </si>
+  <si>
+    <t>4-1-4H</t>
+  </si>
+  <si>
+    <t>4-1-4J</t>
+  </si>
+  <si>
+    <t>4-1-4K</t>
+  </si>
+  <si>
+    <t>4-1-4L</t>
+  </si>
+  <si>
+    <t>4-1-4M</t>
   </si>
 </sst>
 </file>
@@ -553,7 +1808,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -561,13 +1816,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -575,14 +1830,14 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -679,7 +1934,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -875,11 +2130,122 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -892,11 +2258,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -921,17 +2286,28 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -948,6 +2324,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -957,23 +2339,55 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,70 +2453,18 @@
         <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Arial">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Arial" panose="020B0604020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="굴림"/>
+        <a:font script="Hans" typeface="黑体"/>
+        <a:font script="Hant" typeface="微軟正黑體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -1126,23 +2488,41 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" panose="020B0604020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="굴림"/>
+        <a:font script="Hans" typeface="黑体"/>
+        <a:font script="Hant" typeface="微軟正黑體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1314,108 +2694,3819 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE0B9A6-1D84-4DC2-A2D7-C7607081BE8E}">
+  <dimension ref="B1:O38"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="2" max="2" width="6.625" customWidth="1"/>
+    <col min="3" max="3" width="8.625" customWidth="1"/>
+    <col min="4" max="4" width="40.625" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
+    <col min="6" max="6" width="2.625" customWidth="1"/>
+    <col min="7" max="7" width="6.625" customWidth="1"/>
+    <col min="8" max="8" width="8.625" customWidth="1"/>
+    <col min="9" max="9" width="40.625" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="2.625" customWidth="1"/>
+    <col min="12" max="12" width="6.625" customWidth="1"/>
+    <col min="13" max="13" width="8.625" customWidth="1"/>
+    <col min="14" max="14" width="40.625" customWidth="1"/>
+    <col min="15" max="15" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="54" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" s="55"/>
+      <c r="G2" s="70" t="s">
+        <v>250</v>
+      </c>
+      <c r="H2" s="56"/>
+      <c r="I2" s="54" t="s">
+        <v>338</v>
+      </c>
+      <c r="J2" s="55"/>
+      <c r="L2" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="M2" s="56"/>
+      <c r="N2" s="54" t="s">
+        <v>339</v>
+      </c>
+      <c r="O2" s="55"/>
+    </row>
+    <row r="3" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="69" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="I3" s="68" t="s">
+        <v>169</v>
+      </c>
+      <c r="J3" s="69" t="s">
+        <v>203</v>
+      </c>
+      <c r="L3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="M3" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="N3" s="68" t="s">
+        <v>169</v>
+      </c>
+      <c r="O3" s="69" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B4" s="74">
+        <v>1</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>340</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="79"/>
+      <c r="G4" s="85">
+        <v>1</v>
+      </c>
+      <c r="H4" s="75" t="s">
+        <v>374</v>
+      </c>
+      <c r="I4" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="90"/>
+      <c r="L4" s="85">
+        <v>1</v>
+      </c>
+      <c r="M4" s="75" t="s">
+        <v>401</v>
+      </c>
+      <c r="N4" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="90"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B5" s="76">
+        <v>2</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>341</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="80"/>
+      <c r="G5" s="76">
+        <v>2</v>
+      </c>
+      <c r="H5" s="73" t="s">
+        <v>375</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="80"/>
+      <c r="L5" s="76">
+        <v>2</v>
+      </c>
+      <c r="M5" s="73" t="s">
+        <v>400</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="O5" s="80"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B6" s="76">
+        <v>3</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>342</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="80"/>
+      <c r="G6" s="76">
+        <v>3</v>
+      </c>
+      <c r="H6" s="73" t="s">
+        <v>376</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="80"/>
+      <c r="L6" s="76">
+        <v>3</v>
+      </c>
+      <c r="M6" s="73" t="s">
+        <v>402</v>
+      </c>
+      <c r="N6" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="O6" s="80"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B7" s="76">
+        <v>4</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="80"/>
+      <c r="G7" s="76">
+        <v>4</v>
+      </c>
+      <c r="H7" s="73" t="s">
+        <v>377</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J7" s="80"/>
+      <c r="L7" s="76">
+        <v>4</v>
+      </c>
+      <c r="M7" s="73" t="s">
+        <v>403</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="O7" s="80"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B8" s="76">
+        <v>5</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>344</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="80"/>
+      <c r="G8" s="76">
+        <v>5</v>
+      </c>
+      <c r="H8" s="73" t="s">
+        <v>378</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="80"/>
+      <c r="L8" s="76">
+        <v>5</v>
+      </c>
+      <c r="M8" s="73" t="s">
+        <v>404</v>
+      </c>
+      <c r="N8" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="O8" s="80"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B9" s="76">
+        <v>6</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>345</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="80"/>
+      <c r="G9" s="76">
+        <v>6</v>
+      </c>
+      <c r="H9" s="73" t="s">
+        <v>379</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J9" s="80"/>
+      <c r="L9" s="76">
+        <v>6</v>
+      </c>
+      <c r="M9" s="73" t="s">
+        <v>405</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="O9" s="80"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B10" s="76">
+        <v>7</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>346</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="80"/>
+      <c r="G10" s="76">
+        <v>7</v>
+      </c>
+      <c r="H10" s="73" t="s">
+        <v>380</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="80"/>
+      <c r="L10" s="76">
+        <v>7</v>
+      </c>
+      <c r="M10" s="73" t="s">
+        <v>406</v>
+      </c>
+      <c r="N10" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="O10" s="80"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B11" s="76">
+        <v>8</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>347</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="80"/>
+      <c r="G11" s="76">
+        <v>8</v>
+      </c>
+      <c r="H11" s="73" t="s">
+        <v>381</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="80"/>
+      <c r="L11" s="76">
+        <v>8</v>
+      </c>
+      <c r="M11" s="73" t="s">
+        <v>407</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="O11" s="80"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B12" s="76">
+        <v>9</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>348</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="80"/>
+      <c r="G12" s="76">
+        <v>9</v>
+      </c>
+      <c r="H12" s="73" t="s">
+        <v>382</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J12" s="80"/>
+      <c r="L12" s="76">
+        <v>9</v>
+      </c>
+      <c r="M12" s="73" t="s">
+        <v>408</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="O12" s="80"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B13" s="76">
+        <v>10</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>349</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="80"/>
+      <c r="G13" s="76">
+        <v>10</v>
+      </c>
+      <c r="H13" s="73" t="s">
+        <v>383</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="80"/>
+      <c r="L13" s="76">
+        <v>10</v>
+      </c>
+      <c r="M13" s="73" t="s">
+        <v>409</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="O13" s="80"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B14" s="76">
+        <v>11</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="80"/>
+      <c r="G14" s="76">
+        <v>11</v>
+      </c>
+      <c r="H14" s="73" t="s">
+        <v>384</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14" s="80"/>
+      <c r="L14" s="76">
+        <v>11</v>
+      </c>
+      <c r="M14" s="73" t="s">
+        <v>410</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="O14" s="80"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B15" s="76">
+        <v>12</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>351</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="80"/>
+      <c r="G15" s="76">
+        <v>12</v>
+      </c>
+      <c r="H15" s="73" t="s">
+        <v>385</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" s="80"/>
+      <c r="L15" s="76">
+        <v>12</v>
+      </c>
+      <c r="M15" s="73" t="s">
+        <v>411</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="O15" s="80"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B16" s="76">
+        <v>13</v>
+      </c>
+      <c r="C16" s="73" t="s">
+        <v>352</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="80"/>
+      <c r="G16" s="76">
+        <v>13</v>
+      </c>
+      <c r="H16" s="73" t="s">
+        <v>386</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" s="80"/>
+      <c r="L16" s="76">
+        <v>13</v>
+      </c>
+      <c r="M16" s="73" t="s">
+        <v>412</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="O16" s="80"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B17" s="76">
+        <v>14</v>
+      </c>
+      <c r="C17" s="73" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="80"/>
+      <c r="G17" s="76">
+        <v>14</v>
+      </c>
+      <c r="H17" s="73" t="s">
+        <v>387</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J17" s="80"/>
+      <c r="L17" s="76">
+        <v>14</v>
+      </c>
+      <c r="M17" s="73" t="s">
+        <v>413</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O17" s="80"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B18" s="76">
+        <v>15</v>
+      </c>
+      <c r="C18" s="73" t="s">
+        <v>354</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="80"/>
+      <c r="G18" s="76">
+        <v>15</v>
+      </c>
+      <c r="H18" s="73" t="s">
+        <v>388</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="80"/>
+      <c r="L18" s="76">
+        <v>15</v>
+      </c>
+      <c r="M18" s="73" t="s">
+        <v>414</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="O18" s="80"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B19" s="76">
+        <v>16</v>
+      </c>
+      <c r="C19" s="73" t="s">
+        <v>355</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="80"/>
+      <c r="G19" s="76">
+        <v>16</v>
+      </c>
+      <c r="H19" s="73" t="s">
+        <v>389</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J19" s="80"/>
+      <c r="L19" s="76">
+        <v>16</v>
+      </c>
+      <c r="M19" s="73" t="s">
+        <v>415</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="O19" s="80"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B20" s="76">
+        <v>17</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>356</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="80"/>
+      <c r="G20" s="76">
+        <v>17</v>
+      </c>
+      <c r="H20" s="73" t="s">
+        <v>390</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="80"/>
+      <c r="L20" s="76">
+        <v>17</v>
+      </c>
+      <c r="M20" s="73" t="s">
+        <v>416</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="O20" s="80"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B21" s="76">
+        <v>18</v>
+      </c>
+      <c r="C21" s="73" t="s">
+        <v>357</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="80"/>
+      <c r="G21" s="76">
+        <v>18</v>
+      </c>
+      <c r="H21" s="73" t="s">
+        <v>391</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J21" s="80"/>
+      <c r="L21" s="76">
+        <v>18</v>
+      </c>
+      <c r="M21" s="73" t="s">
+        <v>417</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="O21" s="80"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" s="76">
+        <v>19</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>358</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="80"/>
+      <c r="G22" s="76">
+        <v>19</v>
+      </c>
+      <c r="H22" s="73" t="s">
+        <v>392</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" s="80"/>
+      <c r="L22" s="76">
+        <v>19</v>
+      </c>
+      <c r="M22" s="73" t="s">
+        <v>418</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O22" s="80"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B23" s="76">
+        <v>20</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>359</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="80"/>
+      <c r="G23" s="76">
+        <v>20</v>
+      </c>
+      <c r="H23" s="73" t="s">
+        <v>393</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="J23" s="80"/>
+      <c r="L23" s="76">
+        <v>20</v>
+      </c>
+      <c r="M23" s="73" t="s">
+        <v>419</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O23" s="80"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24" s="76">
+        <v>21</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>360</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="80"/>
+      <c r="G24" s="76">
+        <v>21</v>
+      </c>
+      <c r="H24" s="73" t="s">
+        <v>394</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="80"/>
+      <c r="L24" s="76">
+        <v>21</v>
+      </c>
+      <c r="M24" s="73" t="s">
+        <v>420</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="O24" s="80"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B25" s="76">
+        <v>22</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>361</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="80"/>
+      <c r="G25" s="76">
+        <v>22</v>
+      </c>
+      <c r="H25" s="73" t="s">
+        <v>395</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="J25" s="80"/>
+      <c r="L25" s="76">
+        <v>22</v>
+      </c>
+      <c r="M25" s="73" t="s">
+        <v>421</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="O25" s="80"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B26" s="76">
+        <v>23</v>
+      </c>
+      <c r="C26" s="73" t="s">
+        <v>362</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="80"/>
+      <c r="G26" s="76">
+        <v>23</v>
+      </c>
+      <c r="H26" s="73" t="s">
+        <v>396</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J26" s="80"/>
+      <c r="L26" s="76">
+        <v>23</v>
+      </c>
+      <c r="M26" s="73" t="s">
+        <v>422</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O26" s="80"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B27" s="76">
+        <v>24</v>
+      </c>
+      <c r="C27" s="73" t="s">
+        <v>363</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="80"/>
+      <c r="G27" s="76">
+        <v>24</v>
+      </c>
+      <c r="H27" s="73" t="s">
+        <v>397</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="J27" s="80"/>
+      <c r="L27" s="76">
+        <v>24</v>
+      </c>
+      <c r="M27" s="73" t="s">
+        <v>423</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="O27" s="80"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B28" s="76">
+        <v>25</v>
+      </c>
+      <c r="C28" s="73" t="s">
+        <v>364</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="80"/>
+      <c r="G28" s="76">
+        <v>25</v>
+      </c>
+      <c r="H28" s="73" t="s">
+        <v>398</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J28" s="80"/>
+      <c r="L28" s="76">
+        <v>25</v>
+      </c>
+      <c r="M28" s="73" t="s">
+        <v>424</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="O28" s="80"/>
+    </row>
+    <row r="29" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="76">
+        <v>26</v>
+      </c>
+      <c r="C29" s="73" t="s">
+        <v>365</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="80"/>
+      <c r="G29" s="77">
+        <v>26</v>
+      </c>
+      <c r="H29" s="78" t="s">
+        <v>399</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J29" s="81"/>
+      <c r="L29" s="76">
+        <v>26</v>
+      </c>
+      <c r="M29" s="73" t="s">
+        <v>425</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29" s="80"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B30" s="76">
+        <v>27</v>
+      </c>
+      <c r="C30" s="73" t="s">
+        <v>366</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="80"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="64"/>
+      <c r="L30" s="76">
+        <v>27</v>
+      </c>
+      <c r="M30" s="73" t="s">
+        <v>426</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="O30" s="80"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B31" s="76">
+        <v>28</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>367</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="80"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="64"/>
+      <c r="L31" s="76">
+        <v>28</v>
+      </c>
+      <c r="M31" s="73" t="s">
+        <v>427</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="O31" s="80"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B32" s="76">
+        <v>29</v>
+      </c>
+      <c r="C32" s="73" t="s">
+        <v>368</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="80"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="64"/>
+      <c r="L32" s="76">
+        <v>29</v>
+      </c>
+      <c r="M32" s="73" t="s">
+        <v>428</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="O32" s="80"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B33" s="76">
+        <v>30</v>
+      </c>
+      <c r="C33" s="73" t="s">
+        <v>369</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="80"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="65"/>
+      <c r="I33" s="65"/>
+      <c r="J33" s="64"/>
+      <c r="L33" s="76">
+        <v>30</v>
+      </c>
+      <c r="M33" s="73" t="s">
+        <v>429</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="O33" s="80"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B34" s="76">
+        <v>31</v>
+      </c>
+      <c r="C34" s="73" t="s">
+        <v>370</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="80"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="65"/>
+      <c r="J34" s="64"/>
+      <c r="L34" s="76">
+        <v>31</v>
+      </c>
+      <c r="M34" s="73" t="s">
+        <v>430</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="O34" s="80"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B35" s="76">
+        <v>32</v>
+      </c>
+      <c r="C35" s="73" t="s">
+        <v>371</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="80"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="65"/>
+      <c r="I35" s="65"/>
+      <c r="J35" s="64"/>
+      <c r="L35" s="76">
+        <v>32</v>
+      </c>
+      <c r="M35" s="73" t="s">
+        <v>431</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="O35" s="80"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B36" s="76">
+        <v>33</v>
+      </c>
+      <c r="C36" s="73" t="s">
+        <v>372</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="80"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="64"/>
+      <c r="L36" s="76">
+        <v>33</v>
+      </c>
+      <c r="M36" s="73" t="s">
+        <v>432</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="O36" s="80"/>
+    </row>
+    <row r="37" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="77">
+        <v>34</v>
+      </c>
+      <c r="C37" s="78" t="s">
+        <v>373</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="81"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="64"/>
+      <c r="L37" s="77">
+        <v>34</v>
+      </c>
+      <c r="M37" s="78" t="s">
+        <v>433</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="O37" s="81"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B38" s="71"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="64"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="64"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="M4:M37 H4:H29 C4:C37" twoDigitTextYear="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309DF328-187D-46A2-AB7B-03EBEF9F4AB9}">
+  <dimension ref="B1:AD38"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="2" max="2" width="6.625" customWidth="1"/>
+    <col min="3" max="3" width="8.625" customWidth="1"/>
+    <col min="4" max="4" width="40.625" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
+    <col min="6" max="6" width="2.625" customWidth="1"/>
+    <col min="7" max="7" width="6.625" customWidth="1"/>
+    <col min="8" max="8" width="8.625" customWidth="1"/>
+    <col min="9" max="9" width="40.625" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="2.625" customWidth="1"/>
+    <col min="12" max="12" width="6.625" customWidth="1"/>
+    <col min="13" max="13" width="8.625" customWidth="1"/>
+    <col min="14" max="14" width="40.625" customWidth="1"/>
+    <col min="15" max="15" width="10.625" customWidth="1"/>
+    <col min="16" max="16" width="2.625" customWidth="1"/>
+    <col min="17" max="17" width="6.625" customWidth="1"/>
+    <col min="18" max="18" width="8.625" customWidth="1"/>
+    <col min="19" max="19" width="40.625" customWidth="1"/>
+    <col min="20" max="20" width="10.625" customWidth="1"/>
+    <col min="21" max="21" width="2.625" customWidth="1"/>
+    <col min="22" max="22" width="6.625" customWidth="1"/>
+    <col min="23" max="23" width="8.625" customWidth="1"/>
+    <col min="24" max="24" width="40.625" customWidth="1"/>
+    <col min="25" max="25" width="10.625" customWidth="1"/>
+    <col min="26" max="26" width="2.625" customWidth="1"/>
+    <col min="27" max="27" width="6.625" customWidth="1"/>
+    <col min="28" max="28" width="8.625" customWidth="1"/>
+    <col min="29" max="29" width="40.625" customWidth="1"/>
+    <col min="30" max="30" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2" s="55"/>
+      <c r="G2" s="70" t="s">
+        <v>250</v>
+      </c>
+      <c r="H2" s="56"/>
+      <c r="I2" s="54" t="s">
+        <v>249</v>
+      </c>
+      <c r="J2" s="55"/>
+      <c r="L2" s="70" t="s">
+        <v>311</v>
+      </c>
+      <c r="M2" s="56"/>
+      <c r="N2" s="54" t="s">
+        <v>310</v>
+      </c>
+      <c r="O2" s="55"/>
+      <c r="Q2" s="70" t="s">
+        <v>317</v>
+      </c>
+      <c r="R2" s="56"/>
+      <c r="S2" s="54" t="s">
+        <v>318</v>
+      </c>
+      <c r="T2" s="55"/>
+      <c r="V2" s="70" t="s">
+        <v>324</v>
+      </c>
+      <c r="W2" s="56"/>
+      <c r="X2" s="54" t="s">
+        <v>325</v>
+      </c>
+      <c r="Y2" s="55"/>
+      <c r="AA2" s="70" t="s">
+        <v>329</v>
+      </c>
+      <c r="AB2" s="56"/>
+      <c r="AC2" s="54" t="s">
+        <v>330</v>
+      </c>
+      <c r="AD2" s="55"/>
+    </row>
+    <row r="3" spans="2:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="I3" s="69" t="s">
+        <v>169</v>
+      </c>
+      <c r="J3" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="L3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="M3" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="N3" s="69" t="s">
+        <v>169</v>
+      </c>
+      <c r="O3" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="R3" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="S3" s="69" t="s">
+        <v>169</v>
+      </c>
+      <c r="T3" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="V3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="W3" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="X3" s="69" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y3" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA3" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="AB3" s="68" t="s">
+        <v>202</v>
+      </c>
+      <c r="AC3" s="69" t="s">
+        <v>169</v>
+      </c>
+      <c r="AD3" s="63" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="74">
+        <v>1</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="82" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="79"/>
+      <c r="G4" s="74">
+        <v>1</v>
+      </c>
+      <c r="H4" s="75" t="s">
+        <v>280</v>
+      </c>
+      <c r="I4" s="82" t="s">
+        <v>251</v>
+      </c>
+      <c r="J4" s="79"/>
+      <c r="L4" s="74">
+        <v>1</v>
+      </c>
+      <c r="M4" s="75" t="s">
+        <v>315</v>
+      </c>
+      <c r="N4" s="82" t="s">
+        <v>312</v>
+      </c>
+      <c r="O4" s="79"/>
+      <c r="Q4" s="74">
+        <v>1</v>
+      </c>
+      <c r="R4" s="75" t="s">
+        <v>321</v>
+      </c>
+      <c r="S4" s="82" t="s">
+        <v>319</v>
+      </c>
+      <c r="T4" s="79"/>
+      <c r="V4" s="74">
+        <v>1</v>
+      </c>
+      <c r="W4" s="75" t="s">
+        <v>332</v>
+      </c>
+      <c r="X4" s="82" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y4" s="79"/>
+      <c r="AA4" s="86">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="87" t="s">
+        <v>336</v>
+      </c>
+      <c r="AC4" s="88" t="s">
+        <v>331</v>
+      </c>
+      <c r="AD4" s="89"/>
+    </row>
+    <row r="5" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B5" s="76">
+        <v>2</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="83" t="s">
+        <v>174</v>
+      </c>
+      <c r="E5" s="80"/>
+      <c r="G5" s="76">
+        <v>2</v>
+      </c>
+      <c r="H5" s="73" t="s">
+        <v>207</v>
+      </c>
+      <c r="I5" s="83" t="s">
+        <v>251</v>
+      </c>
+      <c r="J5" s="80"/>
+      <c r="L5" s="76">
+        <v>2</v>
+      </c>
+      <c r="M5" s="73" t="s">
+        <v>316</v>
+      </c>
+      <c r="N5" s="83" t="s">
+        <v>313</v>
+      </c>
+      <c r="O5" s="80"/>
+      <c r="Q5" s="76">
+        <v>2</v>
+      </c>
+      <c r="R5" s="73" t="s">
+        <v>322</v>
+      </c>
+      <c r="S5" s="83" t="s">
+        <v>320</v>
+      </c>
+      <c r="T5" s="80"/>
+      <c r="V5" s="76">
+        <v>2</v>
+      </c>
+      <c r="W5" s="73" t="s">
+        <v>333</v>
+      </c>
+      <c r="X5" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y5" s="80"/>
+      <c r="AA5" s="71"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="64"/>
+    </row>
+    <row r="6" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="76">
+        <v>3</v>
+      </c>
+      <c r="C6" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="D6" s="83" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="80"/>
+      <c r="G6" s="76">
+        <v>3</v>
+      </c>
+      <c r="H6" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="I6" s="83" t="s">
+        <v>253</v>
+      </c>
+      <c r="J6" s="80"/>
+      <c r="L6" s="76">
+        <v>3</v>
+      </c>
+      <c r="M6" s="73" t="s">
+        <v>208</v>
+      </c>
+      <c r="N6" s="83" t="s">
+        <v>314</v>
+      </c>
+      <c r="O6" s="80"/>
+      <c r="Q6" s="77">
+        <v>3</v>
+      </c>
+      <c r="R6" s="78" t="s">
+        <v>323</v>
+      </c>
+      <c r="S6" s="84" t="s">
+        <v>182</v>
+      </c>
+      <c r="T6" s="81"/>
+      <c r="V6" s="76">
+        <v>3</v>
+      </c>
+      <c r="W6" s="73" t="s">
+        <v>334</v>
+      </c>
+      <c r="X6" s="83" t="s">
+        <v>328</v>
+      </c>
+      <c r="Y6" s="80"/>
+      <c r="AA6" s="71"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="64"/>
+    </row>
+    <row r="7" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="76">
+        <v>4</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" s="80"/>
+      <c r="G7" s="76">
+        <v>4</v>
+      </c>
+      <c r="H7" s="73" t="s">
+        <v>281</v>
+      </c>
+      <c r="I7" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="J7" s="80"/>
+      <c r="L7" s="77">
+        <v>4</v>
+      </c>
+      <c r="M7" s="78" t="s">
+        <v>212</v>
+      </c>
+      <c r="N7" s="84" t="s">
+        <v>182</v>
+      </c>
+      <c r="O7" s="81"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="65"/>
+      <c r="T7" s="64"/>
+      <c r="V7" s="76">
+        <v>4</v>
+      </c>
+      <c r="W7" s="73" t="s">
+        <v>335</v>
+      </c>
+      <c r="X7" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y7" s="80"/>
+      <c r="AA7" s="71"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="64"/>
+    </row>
+    <row r="8" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="76">
+        <v>5</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="83" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="80"/>
+      <c r="G8" s="76">
+        <v>5</v>
+      </c>
+      <c r="H8" s="73" t="s">
+        <v>282</v>
+      </c>
+      <c r="I8" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="J8" s="80"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="64"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="64"/>
+      <c r="V8" s="77">
+        <v>5</v>
+      </c>
+      <c r="W8" s="78" t="s">
+        <v>209</v>
+      </c>
+      <c r="X8" s="84" t="s">
+        <v>327</v>
+      </c>
+      <c r="Y8" s="81"/>
+      <c r="AA8" s="71"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="64"/>
+    </row>
+    <row r="9" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B9" s="76">
+        <v>6</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="80"/>
+      <c r="G9" s="76">
+        <v>6</v>
+      </c>
+      <c r="H9" s="73" t="s">
+        <v>283</v>
+      </c>
+      <c r="I9" s="83" t="s">
+        <v>256</v>
+      </c>
+      <c r="J9" s="80"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="64"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="65"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="64"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="65"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="64"/>
+      <c r="Z9" s="64"/>
+      <c r="AA9" s="71"/>
+      <c r="AB9" s="65"/>
+      <c r="AC9" s="65"/>
+      <c r="AD9" s="64"/>
+    </row>
+    <row r="10" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B10" s="76">
+        <v>7</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="83" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="80"/>
+      <c r="G10" s="76">
+        <v>7</v>
+      </c>
+      <c r="H10" s="73" t="s">
+        <v>284</v>
+      </c>
+      <c r="I10" s="83" t="s">
+        <v>257</v>
+      </c>
+      <c r="J10" s="80"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="65"/>
+      <c r="O10" s="64"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="65"/>
+      <c r="T10" s="64"/>
+      <c r="V10" s="71"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="64"/>
+      <c r="AA10" s="71"/>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="65"/>
+      <c r="AD10" s="64"/>
+    </row>
+    <row r="11" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B11" s="76">
+        <v>8</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>223</v>
+      </c>
+      <c r="D11" s="83" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="80"/>
+      <c r="G11" s="76">
+        <v>8</v>
+      </c>
+      <c r="H11" s="73" t="s">
+        <v>285</v>
+      </c>
+      <c r="I11" s="83" t="s">
+        <v>258</v>
+      </c>
+      <c r="J11" s="80"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="64"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="65"/>
+      <c r="S11" s="65"/>
+      <c r="T11" s="64"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="65"/>
+      <c r="X11" s="65"/>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="64"/>
+      <c r="AA11" s="71"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="65"/>
+      <c r="AD11" s="64"/>
+    </row>
+    <row r="12" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B12" s="76">
+        <v>9</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" s="80"/>
+      <c r="G12" s="76">
+        <v>9</v>
+      </c>
+      <c r="H12" s="73" t="s">
+        <v>286</v>
+      </c>
+      <c r="I12" s="83" t="s">
+        <v>259</v>
+      </c>
+      <c r="J12" s="80"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="65"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="64"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="64"/>
+      <c r="V12" s="71"/>
+      <c r="W12" s="65"/>
+      <c r="X12" s="65"/>
+      <c r="Y12" s="64"/>
+      <c r="Z12" s="64"/>
+      <c r="AA12" s="71"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="65"/>
+      <c r="AD12" s="64"/>
+    </row>
+    <row r="13" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B13" s="76">
+        <v>10</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>225</v>
+      </c>
+      <c r="D13" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="E13" s="80"/>
+      <c r="G13" s="76">
+        <v>10</v>
+      </c>
+      <c r="H13" s="73" t="s">
+        <v>287</v>
+      </c>
+      <c r="I13" s="83" t="s">
+        <v>260</v>
+      </c>
+      <c r="J13" s="80"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="64"/>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="64"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="64"/>
+      <c r="Z13" s="64"/>
+      <c r="AA13" s="71"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="64"/>
+    </row>
+    <row r="14" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B14" s="76">
+        <v>11</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>226</v>
+      </c>
+      <c r="D14" s="83" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="80"/>
+      <c r="G14" s="76">
+        <v>11</v>
+      </c>
+      <c r="H14" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="I14" s="83" t="s">
+        <v>252</v>
+      </c>
+      <c r="J14" s="80"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="64"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="64"/>
+      <c r="V14" s="71"/>
+      <c r="W14" s="65"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="64"/>
+      <c r="Z14" s="64"/>
+      <c r="AA14" s="71"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="65"/>
+      <c r="AD14" s="64"/>
+    </row>
+    <row r="15" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B15" s="76">
+        <v>12</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>227</v>
+      </c>
+      <c r="D15" s="83" t="s">
+        <v>171</v>
+      </c>
+      <c r="E15" s="80"/>
+      <c r="G15" s="76">
+        <v>12</v>
+      </c>
+      <c r="H15" s="73" t="s">
+        <v>213</v>
+      </c>
+      <c r="I15" s="83" t="s">
+        <v>252</v>
+      </c>
+      <c r="J15" s="80"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="64"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="65"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="64"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="65"/>
+      <c r="X15" s="65"/>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="64"/>
+      <c r="AA15" s="71"/>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="65"/>
+      <c r="AD15" s="64"/>
+    </row>
+    <row r="16" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B16" s="76">
+        <v>13</v>
+      </c>
+      <c r="C16" s="73" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" s="83" t="s">
+        <v>170</v>
+      </c>
+      <c r="E16" s="80"/>
+      <c r="G16" s="76">
+        <v>13</v>
+      </c>
+      <c r="H16" s="73" t="s">
+        <v>289</v>
+      </c>
+      <c r="I16" s="83" t="s">
+        <v>261</v>
+      </c>
+      <c r="J16" s="80"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="65"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="64"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="64"/>
+      <c r="V16" s="71"/>
+      <c r="W16" s="65"/>
+      <c r="X16" s="65"/>
+      <c r="Y16" s="64"/>
+      <c r="Z16" s="64"/>
+      <c r="AA16" s="71"/>
+      <c r="AB16" s="65"/>
+      <c r="AC16" s="65"/>
+      <c r="AD16" s="64"/>
+    </row>
+    <row r="17" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B17" s="76">
+        <v>14</v>
+      </c>
+      <c r="C17" s="73" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="83" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" s="80"/>
+      <c r="G17" s="76">
+        <v>14</v>
+      </c>
+      <c r="H17" s="73" t="s">
+        <v>290</v>
+      </c>
+      <c r="I17" s="83" t="s">
+        <v>261</v>
+      </c>
+      <c r="J17" s="80"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="65"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="64"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="64"/>
+      <c r="V17" s="71"/>
+      <c r="W17" s="65"/>
+      <c r="X17" s="65"/>
+      <c r="Y17" s="64"/>
+      <c r="Z17" s="64"/>
+      <c r="AA17" s="71"/>
+      <c r="AB17" s="65"/>
+      <c r="AC17" s="65"/>
+      <c r="AD17" s="64"/>
+    </row>
+    <row r="18" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B18" s="76">
+        <v>15</v>
+      </c>
+      <c r="C18" s="73" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" s="83" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" s="80"/>
+      <c r="G18" s="76">
+        <v>15</v>
+      </c>
+      <c r="H18" s="73" t="s">
+        <v>216</v>
+      </c>
+      <c r="I18" s="83" t="s">
+        <v>262</v>
+      </c>
+      <c r="J18" s="80"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="64"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="64"/>
+      <c r="V18" s="71"/>
+      <c r="W18" s="65"/>
+      <c r="X18" s="65"/>
+      <c r="Y18" s="64"/>
+      <c r="Z18" s="64"/>
+      <c r="AA18" s="71"/>
+      <c r="AB18" s="65"/>
+      <c r="AC18" s="65"/>
+      <c r="AD18" s="64"/>
+    </row>
+    <row r="19" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B19" s="76">
+        <v>16</v>
+      </c>
+      <c r="C19" s="73" t="s">
+        <v>229</v>
+      </c>
+      <c r="D19" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="E19" s="80"/>
+      <c r="G19" s="76">
+        <v>16</v>
+      </c>
+      <c r="H19" s="73" t="s">
+        <v>291</v>
+      </c>
+      <c r="I19" s="83" t="s">
+        <v>263</v>
+      </c>
+      <c r="J19" s="80"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="64"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="64"/>
+      <c r="V19" s="71"/>
+      <c r="W19" s="65"/>
+      <c r="X19" s="65"/>
+      <c r="Y19" s="64"/>
+      <c r="Z19" s="64"/>
+      <c r="AA19" s="71"/>
+      <c r="AB19" s="65"/>
+      <c r="AC19" s="65"/>
+      <c r="AD19" s="64"/>
+    </row>
+    <row r="20" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B20" s="76">
+        <v>17</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>230</v>
+      </c>
+      <c r="D20" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="E20" s="80"/>
+      <c r="G20" s="76">
+        <v>17</v>
+      </c>
+      <c r="H20" s="73" t="s">
+        <v>292</v>
+      </c>
+      <c r="I20" s="83" t="s">
+        <v>264</v>
+      </c>
+      <c r="J20" s="80"/>
+      <c r="L20" s="71"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="64"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="65"/>
+      <c r="T20" s="64"/>
+      <c r="V20" s="71"/>
+      <c r="W20" s="65"/>
+      <c r="X20" s="65"/>
+      <c r="Y20" s="64"/>
+      <c r="Z20" s="64"/>
+      <c r="AA20" s="71"/>
+      <c r="AB20" s="65"/>
+      <c r="AC20" s="65"/>
+      <c r="AD20" s="64"/>
+    </row>
+    <row r="21" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B21" s="76">
+        <v>18</v>
+      </c>
+      <c r="C21" s="73" t="s">
+        <v>231</v>
+      </c>
+      <c r="D21" s="83" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" s="80"/>
+      <c r="G21" s="76">
+        <v>18</v>
+      </c>
+      <c r="H21" s="73" t="s">
+        <v>293</v>
+      </c>
+      <c r="I21" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="J21" s="80"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="65"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="64"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="64"/>
+      <c r="V21" s="71"/>
+      <c r="W21" s="65"/>
+      <c r="X21" s="65"/>
+      <c r="Y21" s="64"/>
+      <c r="Z21" s="64"/>
+      <c r="AA21" s="71"/>
+      <c r="AB21" s="65"/>
+      <c r="AC21" s="65"/>
+      <c r="AD21" s="64"/>
+    </row>
+    <row r="22" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B22" s="76">
+        <v>19</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>232</v>
+      </c>
+      <c r="D22" s="83" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" s="80"/>
+      <c r="G22" s="76">
+        <v>19</v>
+      </c>
+      <c r="H22" s="73" t="s">
+        <v>294</v>
+      </c>
+      <c r="I22" s="83" t="s">
+        <v>265</v>
+      </c>
+      <c r="J22" s="80"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="64"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="64"/>
+      <c r="V22" s="71"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="64"/>
+      <c r="Z22" s="64"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="64"/>
+    </row>
+    <row r="23" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B23" s="76">
+        <v>20</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>233</v>
+      </c>
+      <c r="D23" s="83" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" s="80"/>
+      <c r="G23" s="76">
+        <v>20</v>
+      </c>
+      <c r="H23" s="73" t="s">
+        <v>295</v>
+      </c>
+      <c r="I23" s="83" t="s">
+        <v>266</v>
+      </c>
+      <c r="J23" s="80"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="65"/>
+      <c r="N23" s="65"/>
+      <c r="O23" s="64"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="65"/>
+      <c r="S23" s="65"/>
+      <c r="T23" s="64"/>
+      <c r="V23" s="71"/>
+      <c r="W23" s="65"/>
+      <c r="X23" s="65"/>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="64"/>
+      <c r="AA23" s="71"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="65"/>
+      <c r="AD23" s="64"/>
+    </row>
+    <row r="24" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B24" s="76">
+        <v>21</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>234</v>
+      </c>
+      <c r="D24" s="83" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" s="80"/>
+      <c r="G24" s="76">
+        <v>21</v>
+      </c>
+      <c r="H24" s="73" t="s">
+        <v>296</v>
+      </c>
+      <c r="I24" s="83" t="s">
+        <v>267</v>
+      </c>
+      <c r="J24" s="80"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="65"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="64"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="65"/>
+      <c r="T24" s="64"/>
+      <c r="V24" s="71"/>
+      <c r="W24" s="65"/>
+      <c r="X24" s="65"/>
+      <c r="Y24" s="64"/>
+      <c r="Z24" s="64"/>
+      <c r="AA24" s="71"/>
+      <c r="AB24" s="65"/>
+      <c r="AC24" s="65"/>
+      <c r="AD24" s="64"/>
+    </row>
+    <row r="25" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B25" s="76">
+        <v>22</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>235</v>
+      </c>
+      <c r="D25" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" s="80"/>
+      <c r="G25" s="76">
+        <v>22</v>
+      </c>
+      <c r="H25" s="73" t="s">
+        <v>297</v>
+      </c>
+      <c r="I25" s="83" t="s">
+        <v>268</v>
+      </c>
+      <c r="J25" s="80"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="64"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="64"/>
+      <c r="V25" s="71"/>
+      <c r="W25" s="65"/>
+      <c r="X25" s="65"/>
+      <c r="Y25" s="64"/>
+      <c r="Z25" s="64"/>
+      <c r="AA25" s="71"/>
+      <c r="AB25" s="65"/>
+      <c r="AC25" s="65"/>
+      <c r="AD25" s="64"/>
+    </row>
+    <row r="26" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B26" s="76">
+        <v>23</v>
+      </c>
+      <c r="C26" s="73" t="s">
+        <v>236</v>
+      </c>
+      <c r="D26" s="83" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="80"/>
+      <c r="G26" s="76">
+        <v>23</v>
+      </c>
+      <c r="H26" s="73" t="s">
+        <v>217</v>
+      </c>
+      <c r="I26" s="83" t="s">
+        <v>269</v>
+      </c>
+      <c r="J26" s="80"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="64"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="65"/>
+      <c r="S26" s="65"/>
+      <c r="T26" s="64"/>
+      <c r="V26" s="71"/>
+      <c r="W26" s="65"/>
+      <c r="X26" s="65"/>
+      <c r="Y26" s="64"/>
+      <c r="Z26" s="64"/>
+      <c r="AA26" s="71"/>
+      <c r="AB26" s="65"/>
+      <c r="AC26" s="65"/>
+      <c r="AD26" s="64"/>
+    </row>
+    <row r="27" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B27" s="76">
+        <v>24</v>
+      </c>
+      <c r="C27" s="73" t="s">
+        <v>237</v>
+      </c>
+      <c r="D27" s="83" t="s">
+        <v>172</v>
+      </c>
+      <c r="E27" s="80"/>
+      <c r="G27" s="76">
+        <v>24</v>
+      </c>
+      <c r="H27" s="73" t="s">
+        <v>298</v>
+      </c>
+      <c r="I27" s="83" t="s">
+        <v>270</v>
+      </c>
+      <c r="J27" s="80"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="64"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="65"/>
+      <c r="S27" s="65"/>
+      <c r="T27" s="64"/>
+      <c r="V27" s="71"/>
+      <c r="W27" s="65"/>
+      <c r="X27" s="65"/>
+      <c r="Y27" s="64"/>
+      <c r="Z27" s="64"/>
+      <c r="AA27" s="71"/>
+      <c r="AB27" s="65"/>
+      <c r="AC27" s="65"/>
+      <c r="AD27" s="64"/>
+    </row>
+    <row r="28" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B28" s="76">
+        <v>25</v>
+      </c>
+      <c r="C28" s="73" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" s="83" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="80"/>
+      <c r="G28" s="76">
+        <v>25</v>
+      </c>
+      <c r="H28" s="73" t="s">
+        <v>299</v>
+      </c>
+      <c r="I28" s="83" t="s">
+        <v>270</v>
+      </c>
+      <c r="J28" s="80"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="64"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="65"/>
+      <c r="S28" s="65"/>
+      <c r="T28" s="64"/>
+      <c r="V28" s="71"/>
+      <c r="W28" s="65"/>
+      <c r="X28" s="65"/>
+      <c r="Y28" s="64"/>
+      <c r="Z28" s="64"/>
+      <c r="AA28" s="71"/>
+      <c r="AB28" s="65"/>
+      <c r="AC28" s="65"/>
+      <c r="AD28" s="64"/>
+    </row>
+    <row r="29" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B29" s="76">
+        <v>26</v>
+      </c>
+      <c r="C29" s="73" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" s="83" t="s">
+        <v>193</v>
+      </c>
+      <c r="E29" s="80"/>
+      <c r="G29" s="76">
+        <v>26</v>
+      </c>
+      <c r="H29" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="I29" s="83" t="s">
+        <v>271</v>
+      </c>
+      <c r="J29" s="80"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="64"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="65"/>
+      <c r="S29" s="65"/>
+      <c r="T29" s="64"/>
+      <c r="V29" s="71"/>
+      <c r="W29" s="65"/>
+      <c r="X29" s="65"/>
+      <c r="Y29" s="64"/>
+      <c r="Z29" s="64"/>
+      <c r="AA29" s="71"/>
+      <c r="AB29" s="65"/>
+      <c r="AC29" s="65"/>
+      <c r="AD29" s="64"/>
+    </row>
+    <row r="30" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B30" s="76">
+        <v>27</v>
+      </c>
+      <c r="C30" s="73" t="s">
+        <v>240</v>
+      </c>
+      <c r="D30" s="83" t="s">
+        <v>194</v>
+      </c>
+      <c r="E30" s="80"/>
+      <c r="G30" s="76">
+        <v>27</v>
+      </c>
+      <c r="H30" s="73" t="s">
+        <v>301</v>
+      </c>
+      <c r="I30" s="83" t="s">
+        <v>272</v>
+      </c>
+      <c r="J30" s="80"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="64"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="65"/>
+      <c r="S30" s="65"/>
+      <c r="T30" s="64"/>
+      <c r="V30" s="71"/>
+      <c r="W30" s="65"/>
+      <c r="X30" s="65"/>
+      <c r="Y30" s="64"/>
+      <c r="Z30" s="64"/>
+      <c r="AA30" s="71"/>
+      <c r="AB30" s="65"/>
+      <c r="AC30" s="65"/>
+      <c r="AD30" s="64"/>
+    </row>
+    <row r="31" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B31" s="76">
+        <v>28</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>241</v>
+      </c>
+      <c r="D31" s="83" t="s">
+        <v>195</v>
+      </c>
+      <c r="E31" s="80"/>
+      <c r="G31" s="76">
+        <v>28</v>
+      </c>
+      <c r="H31" s="73" t="s">
+        <v>302</v>
+      </c>
+      <c r="I31" s="83" t="s">
+        <v>273</v>
+      </c>
+      <c r="J31" s="80"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="65"/>
+      <c r="N31" s="65"/>
+      <c r="O31" s="64"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="65"/>
+      <c r="T31" s="64"/>
+      <c r="V31" s="71"/>
+      <c r="W31" s="65"/>
+      <c r="X31" s="65"/>
+      <c r="Y31" s="64"/>
+      <c r="Z31" s="64"/>
+      <c r="AA31" s="71"/>
+      <c r="AB31" s="65"/>
+      <c r="AC31" s="65"/>
+      <c r="AD31" s="64"/>
+    </row>
+    <row r="32" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B32" s="76">
+        <v>29</v>
+      </c>
+      <c r="C32" s="73" t="s">
+        <v>242</v>
+      </c>
+      <c r="D32" s="83" t="s">
+        <v>196</v>
+      </c>
+      <c r="E32" s="80"/>
+      <c r="G32" s="76">
+        <v>29</v>
+      </c>
+      <c r="H32" s="73" t="s">
+        <v>303</v>
+      </c>
+      <c r="I32" s="83" t="s">
+        <v>274</v>
+      </c>
+      <c r="J32" s="80"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="65"/>
+      <c r="O32" s="64"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="65"/>
+      <c r="S32" s="65"/>
+      <c r="T32" s="64"/>
+      <c r="V32" s="71"/>
+      <c r="W32" s="65"/>
+      <c r="X32" s="65"/>
+      <c r="Y32" s="64"/>
+      <c r="Z32" s="64"/>
+      <c r="AA32" s="71"/>
+      <c r="AB32" s="65"/>
+      <c r="AC32" s="65"/>
+      <c r="AD32" s="64"/>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B33" s="76">
+        <v>30</v>
+      </c>
+      <c r="C33" s="73" t="s">
+        <v>243</v>
+      </c>
+      <c r="D33" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="80"/>
+      <c r="G33" s="76">
+        <v>30</v>
+      </c>
+      <c r="H33" s="73" t="s">
+        <v>304</v>
+      </c>
+      <c r="I33" s="83" t="s">
+        <v>275</v>
+      </c>
+      <c r="J33" s="80"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="65"/>
+      <c r="N33" s="65"/>
+      <c r="O33" s="64"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="65"/>
+      <c r="S33" s="65"/>
+      <c r="T33" s="64"/>
+      <c r="V33" s="71"/>
+      <c r="W33" s="65"/>
+      <c r="X33" s="65"/>
+      <c r="Y33" s="64"/>
+      <c r="Z33" s="64"/>
+      <c r="AA33" s="71"/>
+      <c r="AB33" s="65"/>
+      <c r="AC33" s="65"/>
+      <c r="AD33" s="64"/>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B34" s="76">
+        <v>31</v>
+      </c>
+      <c r="C34" s="73" t="s">
+        <v>244</v>
+      </c>
+      <c r="D34" s="83" t="s">
+        <v>197</v>
+      </c>
+      <c r="E34" s="80"/>
+      <c r="G34" s="76">
+        <v>31</v>
+      </c>
+      <c r="H34" s="73" t="s">
+        <v>305</v>
+      </c>
+      <c r="I34" s="83" t="s">
+        <v>276</v>
+      </c>
+      <c r="J34" s="80"/>
+      <c r="L34" s="71"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="64"/>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="65"/>
+      <c r="T34" s="64"/>
+      <c r="V34" s="71"/>
+      <c r="W34" s="65"/>
+      <c r="X34" s="65"/>
+      <c r="Y34" s="64"/>
+      <c r="Z34" s="64"/>
+      <c r="AA34" s="71"/>
+      <c r="AB34" s="65"/>
+      <c r="AC34" s="65"/>
+      <c r="AD34" s="64"/>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B35" s="76">
+        <v>32</v>
+      </c>
+      <c r="C35" s="73" t="s">
+        <v>245</v>
+      </c>
+      <c r="D35" s="83" t="s">
+        <v>199</v>
+      </c>
+      <c r="E35" s="80"/>
+      <c r="G35" s="76">
+        <v>32</v>
+      </c>
+      <c r="H35" s="73" t="s">
+        <v>306</v>
+      </c>
+      <c r="I35" s="83" t="s">
+        <v>277</v>
+      </c>
+      <c r="J35" s="80"/>
+      <c r="L35" s="71"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="65"/>
+      <c r="O35" s="64"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="65"/>
+      <c r="S35" s="65"/>
+      <c r="T35" s="64"/>
+      <c r="V35" s="71"/>
+      <c r="W35" s="65"/>
+      <c r="X35" s="65"/>
+      <c r="Y35" s="64"/>
+      <c r="Z35" s="64"/>
+      <c r="AA35" s="71"/>
+      <c r="AB35" s="65"/>
+      <c r="AC35" s="65"/>
+      <c r="AD35" s="64"/>
+    </row>
+    <row r="36" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B36" s="76">
+        <v>33</v>
+      </c>
+      <c r="C36" s="72" t="s">
+        <v>246</v>
+      </c>
+      <c r="D36" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="E36" s="80"/>
+      <c r="G36" s="76">
+        <v>33</v>
+      </c>
+      <c r="H36" s="73" t="s">
+        <v>307</v>
+      </c>
+      <c r="I36" s="83" t="s">
+        <v>278</v>
+      </c>
+      <c r="J36" s="80"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="64"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="65"/>
+      <c r="S36" s="65"/>
+      <c r="T36" s="64"/>
+      <c r="V36" s="71"/>
+      <c r="W36" s="65"/>
+      <c r="X36" s="65"/>
+      <c r="Y36" s="64"/>
+      <c r="Z36" s="64"/>
+      <c r="AA36" s="71"/>
+      <c r="AB36" s="65"/>
+      <c r="AC36" s="65"/>
+      <c r="AD36" s="64"/>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B37" s="76">
+        <v>34</v>
+      </c>
+      <c r="C37" s="72" t="s">
+        <v>247</v>
+      </c>
+      <c r="D37" s="83" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" s="80"/>
+      <c r="G37" s="76">
+        <v>34</v>
+      </c>
+      <c r="H37" s="73" t="s">
+        <v>308</v>
+      </c>
+      <c r="I37" s="83" t="s">
+        <v>279</v>
+      </c>
+      <c r="J37" s="80"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="64"/>
+      <c r="Q37" s="71"/>
+      <c r="R37" s="65"/>
+      <c r="S37" s="65"/>
+      <c r="T37" s="64"/>
+      <c r="V37" s="71"/>
+      <c r="W37" s="65"/>
+      <c r="X37" s="65"/>
+      <c r="Y37" s="64"/>
+      <c r="Z37" s="64"/>
+      <c r="AA37" s="71"/>
+      <c r="AB37" s="65"/>
+      <c r="AC37" s="65"/>
+      <c r="AD37" s="64"/>
+    </row>
+    <row r="38" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="77">
+        <v>35</v>
+      </c>
+      <c r="C38" s="66" t="s">
+        <v>248</v>
+      </c>
+      <c r="D38" s="84" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" s="81"/>
+      <c r="G38" s="77">
+        <v>35</v>
+      </c>
+      <c r="H38" s="78" t="s">
+        <v>309</v>
+      </c>
+      <c r="I38" s="84" t="s">
+        <v>279</v>
+      </c>
+      <c r="J38" s="81"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="64"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="65"/>
+      <c r="T38" s="64"/>
+      <c r="V38" s="71"/>
+      <c r="W38" s="65"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="64"/>
+      <c r="Z38" s="64"/>
+      <c r="AA38" s="71"/>
+      <c r="AB38" s="65"/>
+      <c r="AC38" s="65"/>
+      <c r="AD38" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="L2:M2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F7C719E-9FC5-4AC3-AC08-3E5689558DF0}">
+  <dimension ref="B1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="6.625" customWidth="1"/>
+    <col min="3" max="3" width="8.625" customWidth="1"/>
+    <col min="4" max="4" width="40.625" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="54" t="s">
+        <v>434</v>
+      </c>
+      <c r="E2" s="55"/>
+    </row>
+    <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="63" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="74">
+        <v>1</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>447</v>
+      </c>
+      <c r="D4" s="82" t="s">
+        <v>435</v>
+      </c>
+      <c r="E4" s="79"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="76">
+        <v>2</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>448</v>
+      </c>
+      <c r="D5" s="83" t="s">
+        <v>436</v>
+      </c>
+      <c r="E5" s="80"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="76">
+        <v>3</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>449</v>
+      </c>
+      <c r="D6" s="83" t="s">
+        <v>437</v>
+      </c>
+      <c r="E6" s="80"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="76">
+        <v>4</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>450</v>
+      </c>
+      <c r="D7" s="83" t="s">
+        <v>438</v>
+      </c>
+      <c r="E7" s="80"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="76">
+        <v>5</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>451</v>
+      </c>
+      <c r="D8" s="83" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" s="80"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="76">
+        <v>6</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>452</v>
+      </c>
+      <c r="D9" s="83" t="s">
+        <v>440</v>
+      </c>
+      <c r="E9" s="80"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="76">
+        <v>7</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>453</v>
+      </c>
+      <c r="D10" s="83" t="s">
+        <v>442</v>
+      </c>
+      <c r="E10" s="80"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="76">
+        <v>8</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>454</v>
+      </c>
+      <c r="D11" s="83" t="s">
+        <v>441</v>
+      </c>
+      <c r="E11" s="80"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="76">
+        <v>9</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>455</v>
+      </c>
+      <c r="D12" s="83" t="s">
+        <v>443</v>
+      </c>
+      <c r="E12" s="80"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="76">
+        <v>10</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>456</v>
+      </c>
+      <c r="D13" s="83" t="s">
+        <v>444</v>
+      </c>
+      <c r="E13" s="80"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="76">
+        <v>11</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>457</v>
+      </c>
+      <c r="D14" s="83" t="s">
+        <v>445</v>
+      </c>
+      <c r="E14" s="80"/>
+    </row>
+    <row r="15" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="77">
+        <v>12</v>
+      </c>
+      <c r="C15" s="78" t="s">
+        <v>458</v>
+      </c>
+      <c r="D15" s="84" t="s">
+        <v>446</v>
+      </c>
+      <c r="E15" s="81"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="71"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="64"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="71"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="64"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="71"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="64"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="71"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="64"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="71"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="64"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="71"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="64"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22" s="71"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="64"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="71"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="64"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="71"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="64"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="71"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="64"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="71"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="64"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="71"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="64"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B28" s="71"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="64"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B29" s="71"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="64"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B30" s="71"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="64"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B31" s="71"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="64"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B32" s="71"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="64"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B33" s="71"/>
+      <c r="C33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="64"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B34" s="71"/>
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="64"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="71"/>
+      <c r="C35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="64"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="71"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="64"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="71"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="64"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B38" s="71"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C4:C15" twoDigitTextYear="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB64265-B021-4A0F-85F6-5ED55576D049}">
+  <dimension ref="B1:E51"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="6.625" customWidth="1"/>
+    <col min="3" max="3" width="8.625" customWidth="1"/>
+    <col min="4" max="4" width="40.625" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2" s="55"/>
+    </row>
+    <row r="3" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="63" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="74" t="s">
+        <v>459</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>538</v>
+      </c>
+      <c r="D4" s="82" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="79"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="76" t="s">
+        <v>460</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>539</v>
+      </c>
+      <c r="D5" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="80"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="76" t="s">
+        <v>461</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>540</v>
+      </c>
+      <c r="D6" s="83" t="s">
+        <v>507</v>
+      </c>
+      <c r="E6" s="80"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="76" t="s">
+        <v>462</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>541</v>
+      </c>
+      <c r="D7" s="83" t="s">
+        <v>508</v>
+      </c>
+      <c r="E7" s="80"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="76" t="s">
+        <v>463</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>542</v>
+      </c>
+      <c r="D8" s="83" t="s">
+        <v>509</v>
+      </c>
+      <c r="E8" s="80"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="76" t="s">
+        <v>464</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>543</v>
+      </c>
+      <c r="D9" s="83" t="s">
+        <v>510</v>
+      </c>
+      <c r="E9" s="80"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="76" t="s">
+        <v>465</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>544</v>
+      </c>
+      <c r="D10" s="83" t="s">
+        <v>511</v>
+      </c>
+      <c r="E10" s="80"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="76" t="s">
+        <v>466</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>545</v>
+      </c>
+      <c r="D11" s="83" t="s">
+        <v>512</v>
+      </c>
+      <c r="E11" s="80"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="76" t="s">
+        <v>467</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>546</v>
+      </c>
+      <c r="D12" s="83" t="s">
+        <v>513</v>
+      </c>
+      <c r="E12" s="80"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="76" t="s">
+        <v>468</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>547</v>
+      </c>
+      <c r="D13" s="83" t="s">
+        <v>514</v>
+      </c>
+      <c r="E13" s="80"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="76" t="s">
+        <v>469</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>548</v>
+      </c>
+      <c r="D14" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="E14" s="80"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="76" t="s">
+        <v>470</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>549</v>
+      </c>
+      <c r="D15" s="83" t="s">
+        <v>515</v>
+      </c>
+      <c r="E15" s="80"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="76" t="s">
+        <v>471</v>
+      </c>
+      <c r="C16" s="73" t="s">
+        <v>550</v>
+      </c>
+      <c r="D16" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" s="80"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="76" t="s">
+        <v>472</v>
+      </c>
+      <c r="C17" s="73" t="s">
+        <v>551</v>
+      </c>
+      <c r="D17" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="80"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="76" t="s">
+        <v>473</v>
+      </c>
+      <c r="C18" s="73" t="s">
+        <v>552</v>
+      </c>
+      <c r="D18" s="83" t="s">
+        <v>516</v>
+      </c>
+      <c r="E18" s="80"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="76" t="s">
+        <v>474</v>
+      </c>
+      <c r="C19" s="73" t="s">
+        <v>553</v>
+      </c>
+      <c r="D19" s="83" t="s">
+        <v>517</v>
+      </c>
+      <c r="E19" s="80"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="76" t="s">
+        <v>475</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>554</v>
+      </c>
+      <c r="D20" s="83" t="s">
+        <v>518</v>
+      </c>
+      <c r="E20" s="80"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="76" t="s">
+        <v>476</v>
+      </c>
+      <c r="C21" s="73" t="s">
+        <v>555</v>
+      </c>
+      <c r="D21" s="83" t="s">
+        <v>519</v>
+      </c>
+      <c r="E21" s="80"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22" s="76" t="s">
+        <v>477</v>
+      </c>
+      <c r="C22" s="73" t="s">
+        <v>556</v>
+      </c>
+      <c r="D22" s="83" t="s">
+        <v>520</v>
+      </c>
+      <c r="E22" s="80"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="76" t="s">
+        <v>478</v>
+      </c>
+      <c r="C23" s="73" t="s">
+        <v>557</v>
+      </c>
+      <c r="D23" s="83" t="s">
+        <v>521</v>
+      </c>
+      <c r="E23" s="80"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="76" t="s">
+        <v>479</v>
+      </c>
+      <c r="C24" s="73" t="s">
+        <v>558</v>
+      </c>
+      <c r="D24" s="83" t="s">
+        <v>522</v>
+      </c>
+      <c r="E24" s="80"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="76" t="s">
+        <v>480</v>
+      </c>
+      <c r="C25" s="73" t="s">
+        <v>559</v>
+      </c>
+      <c r="D25" s="83" t="s">
+        <v>523</v>
+      </c>
+      <c r="E25" s="80"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="76" t="s">
+        <v>481</v>
+      </c>
+      <c r="C26" s="73" t="s">
+        <v>560</v>
+      </c>
+      <c r="D26" s="83"/>
+      <c r="E26" s="80"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="76" t="s">
+        <v>482</v>
+      </c>
+      <c r="C27" s="73" t="s">
+        <v>561</v>
+      </c>
+      <c r="D27" s="83"/>
+      <c r="E27" s="80"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B28" s="76" t="s">
+        <v>483</v>
+      </c>
+      <c r="C28" s="73" t="s">
+        <v>562</v>
+      </c>
+      <c r="D28" s="83" t="s">
+        <v>524</v>
+      </c>
+      <c r="E28" s="80"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B29" s="76" t="s">
+        <v>484</v>
+      </c>
+      <c r="C29" s="73" t="s">
+        <v>563</v>
+      </c>
+      <c r="D29" s="83" t="s">
+        <v>182</v>
+      </c>
+      <c r="E29" s="80"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B30" s="76" t="s">
+        <v>485</v>
+      </c>
+      <c r="C30" s="73" t="s">
+        <v>564</v>
+      </c>
+      <c r="D30" s="83" t="s">
+        <v>525</v>
+      </c>
+      <c r="E30" s="80"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B31" s="76" t="s">
+        <v>486</v>
+      </c>
+      <c r="C31" s="73" t="s">
+        <v>565</v>
+      </c>
+      <c r="D31" s="83" t="s">
+        <v>526</v>
+      </c>
+      <c r="E31" s="80"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B32" s="76" t="s">
+        <v>487</v>
+      </c>
+      <c r="C32" s="73" t="s">
+        <v>566</v>
+      </c>
+      <c r="D32" s="83" t="s">
+        <v>527</v>
+      </c>
+      <c r="E32" s="80"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B33" s="76" t="s">
+        <v>488</v>
+      </c>
+      <c r="C33" s="73" t="s">
+        <v>567</v>
+      </c>
+      <c r="D33" s="83"/>
+      <c r="E33" s="80"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B34" s="76" t="s">
+        <v>489</v>
+      </c>
+      <c r="C34" s="73" t="s">
+        <v>568</v>
+      </c>
+      <c r="D34" s="83" t="s">
+        <v>529</v>
+      </c>
+      <c r="E34" s="80"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="76" t="s">
+        <v>490</v>
+      </c>
+      <c r="C35" s="73" t="s">
+        <v>569</v>
+      </c>
+      <c r="D35" s="83" t="s">
+        <v>528</v>
+      </c>
+      <c r="E35" s="80"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="76" t="s">
+        <v>491</v>
+      </c>
+      <c r="C36" s="73" t="s">
+        <v>570</v>
+      </c>
+      <c r="D36" s="83" t="s">
+        <v>530</v>
+      </c>
+      <c r="E36" s="80"/>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="76" t="s">
+        <v>492</v>
+      </c>
+      <c r="C37" s="73" t="s">
+        <v>571</v>
+      </c>
+      <c r="D37" s="83" t="s">
+        <v>531</v>
+      </c>
+      <c r="E37" s="80"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B38" s="76" t="s">
+        <v>493</v>
+      </c>
+      <c r="C38" s="73" t="s">
+        <v>572</v>
+      </c>
+      <c r="D38" s="83"/>
+      <c r="E38" s="80"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="76" t="s">
+        <v>494</v>
+      </c>
+      <c r="C39" s="73" t="s">
+        <v>573</v>
+      </c>
+      <c r="D39" s="83"/>
+      <c r="E39" s="80"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="76" t="s">
+        <v>495</v>
+      </c>
+      <c r="C40" s="73" t="s">
+        <v>574</v>
+      </c>
+      <c r="D40" s="83" t="s">
+        <v>532</v>
+      </c>
+      <c r="E40" s="80"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B41" s="91" t="s">
+        <v>496</v>
+      </c>
+      <c r="C41" s="73" t="s">
+        <v>575</v>
+      </c>
+      <c r="D41" s="83" t="s">
+        <v>533</v>
+      </c>
+      <c r="E41" s="80"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="91" t="s">
+        <v>497</v>
+      </c>
+      <c r="C42" s="73" t="s">
+        <v>576</v>
+      </c>
+      <c r="D42" s="83"/>
+      <c r="E42" s="80"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="91" t="s">
+        <v>498</v>
+      </c>
+      <c r="C43" s="73" t="s">
+        <v>577</v>
+      </c>
+      <c r="D43" s="83"/>
+      <c r="E43" s="80"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="91" t="s">
+        <v>499</v>
+      </c>
+      <c r="C44" s="73" t="s">
+        <v>578</v>
+      </c>
+      <c r="D44" s="83"/>
+      <c r="E44" s="80"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B45" s="91" t="s">
+        <v>500</v>
+      </c>
+      <c r="C45" s="73" t="s">
+        <v>579</v>
+      </c>
+      <c r="D45" s="83"/>
+      <c r="E45" s="80"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B46" s="91" t="s">
+        <v>501</v>
+      </c>
+      <c r="C46" s="73" t="s">
+        <v>580</v>
+      </c>
+      <c r="D46" s="83"/>
+      <c r="E46" s="80"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B47" s="91" t="s">
+        <v>502</v>
+      </c>
+      <c r="C47" s="73" t="s">
+        <v>581</v>
+      </c>
+      <c r="D47" s="83" t="s">
+        <v>534</v>
+      </c>
+      <c r="E47" s="80"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B48" s="91" t="s">
+        <v>503</v>
+      </c>
+      <c r="C48" s="73" t="s">
+        <v>582</v>
+      </c>
+      <c r="D48" s="83" t="s">
+        <v>535</v>
+      </c>
+      <c r="E48" s="80"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="91" t="s">
+        <v>504</v>
+      </c>
+      <c r="C49" s="73" t="s">
+        <v>583</v>
+      </c>
+      <c r="D49" s="83" t="s">
+        <v>536</v>
+      </c>
+      <c r="E49" s="80"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="91" t="s">
+        <v>505</v>
+      </c>
+      <c r="C50" s="73" t="s">
+        <v>584</v>
+      </c>
+      <c r="D50" s="83" t="s">
+        <v>537</v>
+      </c>
+      <c r="E50" s="80"/>
+    </row>
+    <row r="51" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="92" t="s">
+        <v>506</v>
+      </c>
+      <c r="C51" s="78" t="s">
+        <v>585</v>
+      </c>
+      <c r="D51" s="84" t="s">
+        <v>537</v>
+      </c>
+      <c r="E51" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A72A9D2-AA38-49C5-BA11-754D224F49DA}">
   <dimension ref="B1:R38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" customWidth="1"/>
-    <col min="11" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="2.7109375" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" customWidth="1"/>
-    <col min="15" max="15" width="24.7109375" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" customWidth="1"/>
-    <col min="17" max="18" width="4.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.375" customWidth="1"/>
+    <col min="2" max="2" width="8.625" customWidth="1"/>
+    <col min="3" max="3" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="16.625" customWidth="1"/>
+    <col min="5" max="6" width="4.625" customWidth="1"/>
+    <col min="7" max="7" width="2.625" customWidth="1"/>
+    <col min="8" max="8" width="8.625" customWidth="1"/>
+    <col min="9" max="9" width="20.625" customWidth="1"/>
+    <col min="10" max="10" width="16.625" customWidth="1"/>
+    <col min="11" max="12" width="4.625" customWidth="1"/>
+    <col min="13" max="13" width="2.625" customWidth="1"/>
+    <col min="14" max="14" width="8.625" customWidth="1"/>
+    <col min="15" max="15" width="24.625" customWidth="1"/>
+    <col min="16" max="16" width="16.625" customWidth="1"/>
+    <col min="17" max="18" width="4.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="24" x14ac:dyDescent="0.4">
-      <c r="B1" s="62" t="s">
+    <row r="1" spans="2:18" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-    </row>
-    <row r="2" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+    </row>
+    <row r="2" spans="2:18" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="43"/>
-      <c r="H3" s="41" t="s">
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55"/>
+      <c r="H3" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="43"/>
-      <c r="N3" s="44" t="s">
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="55"/>
+      <c r="N3" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="46"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="60"/>
     </row>
     <row r="4" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="40"/>
-      <c r="H4" s="37" t="s">
+      <c r="E4" s="51"/>
+      <c r="F4" s="52"/>
+      <c r="H4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="35"/>
-      <c r="L4" s="36"/>
-      <c r="N4" s="37" t="s">
+      <c r="K4" s="56"/>
+      <c r="L4" s="57"/>
+      <c r="N4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="O4" s="38" t="s">
+      <c r="O4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="35" t="s">
+      <c r="P4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="36"/>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q4" s="56"/>
+      <c r="R4" s="57"/>
+    </row>
+    <row r="5" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1425,8 +6516,8 @@
       <c r="D5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="13"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="12"/>
       <c r="H5" s="2">
         <v>1</v>
       </c>
@@ -1436,8 +6527,8 @@
       <c r="J5" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K5" s="48"/>
-      <c r="L5" s="49"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="37"/>
       <c r="N5" s="2">
         <v>1</v>
       </c>
@@ -1447,10 +6538,10 @@
       <c r="P5" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="57"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q5" s="44"/>
+      <c r="R5" s="45"/>
+    </row>
+    <row r="6" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B6" s="5">
         <v>2</v>
       </c>
@@ -1460,7 +6551,7 @@
       <c r="D6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="13"/>
       <c r="F6" s="7"/>
       <c r="H6" s="5">
         <v>2</v>
@@ -1471,8 +6562,8 @@
       <c r="J6" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="32"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="31"/>
       <c r="N6" s="5">
         <v>2</v>
       </c>
@@ -1482,10 +6573,10 @@
       <c r="P6" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="20"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q6" s="38"/>
+      <c r="R6" s="19"/>
+    </row>
+    <row r="7" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B7" s="5">
         <v>3</v>
       </c>
@@ -1495,8 +6586,8 @@
       <c r="D7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="16"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15"/>
       <c r="H7" s="5">
         <v>3</v>
       </c>
@@ -1506,21 +6597,21 @@
       <c r="J7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="K7" s="50"/>
-      <c r="L7" s="51"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="39"/>
       <c r="N7" s="5">
         <v>3</v>
       </c>
-      <c r="O7" s="55" t="s">
+      <c r="O7" s="43" t="s">
         <v>118</v>
       </c>
       <c r="P7" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="58"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q7" s="38"/>
+      <c r="R7" s="46"/>
+    </row>
+    <row r="8" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B8" s="5">
         <v>4</v>
       </c>
@@ -1530,8 +6621,8 @@
       <c r="D8" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
       <c r="H8" s="5">
         <v>4</v>
       </c>
@@ -1541,8 +6632,8 @@
       <c r="J8" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="K8" s="50"/>
-      <c r="L8" s="18"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="17"/>
       <c r="N8" s="5">
         <v>4</v>
       </c>
@@ -1552,10 +6643,10 @@
       <c r="P8" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="16"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q8" s="38"/>
+      <c r="R8" s="15"/>
+    </row>
+    <row r="9" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1565,8 +6656,8 @@
       <c r="D9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="19"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="18"/>
       <c r="H9" s="5">
         <v>5</v>
       </c>
@@ -1576,21 +6667,21 @@
       <c r="J9" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="K9" s="50"/>
-      <c r="L9" s="21"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="20"/>
       <c r="N9" s="5">
         <v>5</v>
       </c>
-      <c r="O9" s="55" t="s">
+      <c r="O9" s="43" t="s">
         <v>120</v>
       </c>
       <c r="P9" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="32"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q9" s="38"/>
+      <c r="R9" s="31"/>
+    </row>
+    <row r="10" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B10" s="5">
         <v>6</v>
       </c>
@@ -1600,8 +6691,8 @@
       <c r="D10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="20"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="19"/>
       <c r="H10" s="5">
         <v>6</v>
       </c>
@@ -1611,8 +6702,8 @@
       <c r="J10" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="K10" s="50"/>
-      <c r="L10" s="26"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="25"/>
       <c r="N10" s="5">
         <v>6</v>
       </c>
@@ -1622,10 +6713,10 @@
       <c r="P10" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="Q10" s="50"/>
+      <c r="Q10" s="38"/>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>7</v>
       </c>
@@ -1635,7 +6726,7 @@
       <c r="D11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="17"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="7"/>
       <c r="H11" s="5">
         <v>7</v>
@@ -1646,21 +6737,21 @@
       <c r="J11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="25"/>
-      <c r="L11" s="16"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="15"/>
       <c r="N11" s="5">
         <v>7</v>
       </c>
-      <c r="O11" s="55" t="s">
+      <c r="O11" s="43" t="s">
         <v>122</v>
       </c>
       <c r="P11" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="Q11" s="50"/>
-      <c r="R11" s="29"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q11" s="38"/>
+      <c r="R11" s="28"/>
+    </row>
+    <row r="12" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B12" s="5">
         <v>8</v>
       </c>
@@ -1670,8 +6761,8 @@
       <c r="D12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="21"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="20"/>
       <c r="H12" s="5">
         <v>8</v>
       </c>
@@ -1681,8 +6772,8 @@
       <c r="J12" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="K12" s="22"/>
-      <c r="L12" s="29"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="28"/>
       <c r="N12" s="5">
         <v>8</v>
       </c>
@@ -1692,10 +6783,10 @@
       <c r="P12" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="29"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q12" s="13"/>
+      <c r="R12" s="28"/>
+    </row>
+    <row r="13" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B13" s="5">
         <v>9</v>
       </c>
@@ -1705,8 +6796,8 @@
       <c r="D13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="15"/>
       <c r="H13" s="5">
         <v>9</v>
       </c>
@@ -1716,7 +6807,7 @@
       <c r="J13" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="K13" s="22"/>
+      <c r="K13" s="21"/>
       <c r="L13" s="7"/>
       <c r="N13" s="5">
         <v>9</v>
@@ -1727,10 +6818,10 @@
       <c r="P13" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="16"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q13" s="13"/>
+      <c r="R13" s="15"/>
+    </row>
+    <row r="14" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B14" s="5">
         <v>10</v>
       </c>
@@ -1740,8 +6831,8 @@
       <c r="D14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="16"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
       <c r="H14" s="5">
         <v>10</v>
       </c>
@@ -1751,8 +6842,8 @@
       <c r="J14" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="K14" s="52"/>
-      <c r="L14" s="16"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="15"/>
       <c r="N14" s="5">
         <v>10</v>
       </c>
@@ -1762,10 +6853,10 @@
       <c r="P14" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="58"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q14" s="27"/>
+      <c r="R14" s="46"/>
+    </row>
+    <row r="15" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B15" s="5">
         <v>11</v>
       </c>
@@ -1775,7 +6866,7 @@
       <c r="D15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="15"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="7"/>
       <c r="H15" s="5">
         <v>11</v>
@@ -1786,8 +6877,8 @@
       <c r="J15" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="K15" s="52"/>
-      <c r="L15" s="21"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="20"/>
       <c r="N15" s="5">
         <v>11</v>
       </c>
@@ -1797,10 +6888,10 @@
       <c r="P15" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="51"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q15" s="13"/>
+      <c r="R15" s="39"/>
+    </row>
+    <row r="16" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B16" s="5">
         <v>12</v>
       </c>
@@ -1810,8 +6901,8 @@
       <c r="D16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="20"/>
       <c r="H16" s="5">
         <v>12</v>
       </c>
@@ -1821,8 +6912,8 @@
       <c r="J16" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="K16" s="52"/>
-      <c r="L16" s="23"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="22"/>
       <c r="N16" s="5">
         <v>12</v>
       </c>
@@ -1832,10 +6923,10 @@
       <c r="P16" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="21"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q16" s="13"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B17" s="5">
         <v>13</v>
       </c>
@@ -1845,8 +6936,8 @@
       <c r="D17" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="19"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="18"/>
       <c r="H17" s="5">
         <v>13</v>
       </c>
@@ -1856,7 +6947,7 @@
       <c r="J17" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K17" s="52"/>
+      <c r="K17" s="40"/>
       <c r="L17" s="1"/>
       <c r="N17" s="5">
         <v>13</v>
@@ -1867,10 +6958,10 @@
       <c r="P17" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="51"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q17" s="40"/>
+      <c r="R17" s="39"/>
+    </row>
+    <row r="18" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B18" s="5">
         <v>14</v>
       </c>
@@ -1880,8 +6971,8 @@
       <c r="D18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="22"/>
       <c r="H18" s="5">
         <v>14</v>
       </c>
@@ -1891,7 +6982,7 @@
       <c r="J18" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="K18" s="54"/>
+      <c r="K18" s="42"/>
       <c r="L18" s="7"/>
       <c r="N18" s="5">
         <v>14</v>
@@ -1902,10 +6993,10 @@
       <c r="P18" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="Q18" s="52"/>
-      <c r="R18" s="18"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q18" s="40"/>
+      <c r="R18" s="17"/>
+    </row>
+    <row r="19" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B19" s="5">
         <v>15</v>
       </c>
@@ -1915,8 +7006,8 @@
       <c r="D19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="24"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="23"/>
       <c r="H19" s="5">
         <v>15</v>
       </c>
@@ -1926,8 +7017,8 @@
       <c r="J19" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K19" s="28"/>
-      <c r="L19" s="32"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="31"/>
       <c r="N19" s="5">
         <v>15</v>
       </c>
@@ -1937,10 +7028,10 @@
       <c r="P19" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="Q19" s="52"/>
-      <c r="R19" s="32"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q19" s="40"/>
+      <c r="R19" s="31"/>
+    </row>
+    <row r="20" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B20" s="5">
         <v>16</v>
       </c>
@@ -1950,8 +7041,8 @@
       <c r="D20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="20"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="19"/>
       <c r="H20" s="5">
         <v>16</v>
       </c>
@@ -1961,8 +7052,8 @@
       <c r="J20" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="K20" s="54"/>
-      <c r="L20" s="18"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="17"/>
       <c r="N20" s="5">
         <v>16</v>
       </c>
@@ -1972,10 +7063,10 @@
       <c r="P20" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="Q20" s="52"/>
-      <c r="R20" s="61"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q20" s="40"/>
+      <c r="R20" s="49"/>
+    </row>
+    <row r="21" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B21" s="5">
         <v>17</v>
       </c>
@@ -1985,8 +7076,8 @@
       <c r="D21" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="18"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="17"/>
       <c r="H21" s="5">
         <v>17</v>
       </c>
@@ -1996,8 +7087,8 @@
       <c r="J21" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K21" s="54"/>
-      <c r="L21" s="26"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="25"/>
       <c r="N21" s="5">
         <v>17</v>
       </c>
@@ -2007,10 +7098,10 @@
       <c r="P21" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="Q21" s="52"/>
-      <c r="R21" s="20"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q21" s="40"/>
+      <c r="R21" s="19"/>
+    </row>
+    <row r="22" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B22" s="5">
         <v>18</v>
       </c>
@@ -2020,8 +7111,8 @@
       <c r="D22" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="26"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="25"/>
       <c r="H22" s="5">
         <v>18</v>
       </c>
@@ -2031,8 +7122,8 @@
       <c r="J22" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="K22" s="54"/>
-      <c r="L22" s="29"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="28"/>
       <c r="N22" s="5">
         <v>18</v>
       </c>
@@ -2042,10 +7133,10 @@
       <c r="P22" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="Q22" s="54"/>
+      <c r="Q22" s="42"/>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B23" s="5">
         <v>19</v>
       </c>
@@ -2055,8 +7146,8 @@
       <c r="D23" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="26"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="25"/>
       <c r="H23" s="5">
         <v>19</v>
       </c>
@@ -2066,8 +7157,8 @@
       <c r="J23" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="K23" s="54"/>
-      <c r="L23" s="19"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="18"/>
       <c r="N23" s="5">
         <v>19</v>
       </c>
@@ -2077,10 +7168,10 @@
       <c r="P23" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="18"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q23" s="42"/>
+      <c r="R23" s="17"/>
+    </row>
+    <row r="24" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B24" s="5">
         <v>20</v>
       </c>
@@ -2090,8 +7181,8 @@
       <c r="D24" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="19"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="18"/>
       <c r="H24" s="5">
         <v>20</v>
       </c>
@@ -2101,8 +7192,8 @@
       <c r="J24" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K24" s="28"/>
-      <c r="L24" s="32"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="31"/>
       <c r="N24" s="5">
         <v>20</v>
       </c>
@@ -2112,21 +7203,21 @@
       <c r="P24" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="Q24" s="54"/>
-      <c r="R24" s="61"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q24" s="42"/>
+      <c r="R24" s="49"/>
+    </row>
+    <row r="25" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B25" s="5">
         <v>21</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="20"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="19"/>
       <c r="H25" s="5">
         <v>21</v>
       </c>
@@ -2136,8 +7227,8 @@
       <c r="J25" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="K25" s="31"/>
-      <c r="L25" s="18"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="17"/>
       <c r="N25" s="5">
         <v>21</v>
       </c>
@@ -2147,21 +7238,21 @@
       <c r="P25" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="Q25" s="54"/>
-      <c r="R25" s="29"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q25" s="42"/>
+      <c r="R25" s="28"/>
+    </row>
+    <row r="26" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B26" s="5">
         <v>22</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="18"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="17"/>
       <c r="H26" s="5">
         <v>22</v>
       </c>
@@ -2171,8 +7262,8 @@
       <c r="J26" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="K26" s="27"/>
-      <c r="L26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="25"/>
       <c r="N26" s="5">
         <v>22</v>
       </c>
@@ -2182,21 +7273,21 @@
       <c r="P26" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="Q26" s="54"/>
-      <c r="R26" s="19"/>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q26" s="42"/>
+      <c r="R26" s="18"/>
+    </row>
+    <row r="27" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B27" s="5">
         <v>23</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="25"/>
-      <c r="F27" s="23"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="22"/>
       <c r="H27" s="5">
         <v>23</v>
       </c>
@@ -2206,7 +7297,7 @@
       <c r="J27" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="K27" s="27"/>
+      <c r="K27" s="26"/>
       <c r="L27" s="7"/>
       <c r="N27" s="5">
         <v>23</v>
@@ -2217,21 +7308,21 @@
       <c r="P27" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="32"/>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q27" s="27"/>
+      <c r="R27" s="31"/>
+    </row>
+    <row r="28" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B28" s="5">
         <v>24</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="19"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="18"/>
       <c r="H28" s="5">
         <v>24</v>
       </c>
@@ -2241,8 +7332,8 @@
       <c r="J28" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="K28" s="30"/>
-      <c r="L28" s="32"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="31"/>
       <c r="N28" s="5">
         <v>24</v>
       </c>
@@ -2252,21 +7343,21 @@
       <c r="P28" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="21"/>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q28" s="42"/>
+      <c r="R28" s="20"/>
+    </row>
+    <row r="29" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B29" s="5">
         <v>25</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="27"/>
-      <c r="F29" s="20"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="19"/>
       <c r="H29" s="5">
         <v>25</v>
       </c>
@@ -2276,8 +7367,8 @@
       <c r="J29" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="K29" s="30"/>
-      <c r="L29" s="21"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="20"/>
       <c r="N29" s="5">
         <v>25</v>
       </c>
@@ -2287,32 +7378,32 @@
       <c r="P29" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="Q29" s="54"/>
-      <c r="R29" s="20"/>
-    </row>
-    <row r="30" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q29" s="42"/>
+      <c r="R29" s="19"/>
+    </row>
+    <row r="30" spans="2:18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="5">
         <v>26</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29"/>
-      <c r="H30" s="9">
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="H30" s="8">
         <v>26</v>
       </c>
-      <c r="I30" s="47" t="s">
+      <c r="I30" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="J30" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="K30" s="33"/>
-      <c r="L30" s="53"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="41"/>
       <c r="N30" s="5">
         <v>26</v>
       </c>
@@ -2322,21 +7413,21 @@
       <c r="P30" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="29"/>
-    </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q30" s="27"/>
+      <c r="R30" s="28"/>
+    </row>
+    <row r="31" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B31" s="5">
         <v>27</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E31" s="30"/>
-      <c r="F31" s="19"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="18"/>
       <c r="N31" s="5">
         <v>27</v>
       </c>
@@ -2346,20 +7437,20 @@
       <c r="P31" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="51"/>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q31" s="29"/>
+      <c r="R31" s="39"/>
+    </row>
+    <row r="32" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B32" s="5">
         <v>28</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E32" s="30"/>
+      <c r="E32" s="29"/>
       <c r="F32" s="7"/>
       <c r="N32" s="5">
         <v>28</v>
@@ -2370,21 +7461,21 @@
       <c r="P32" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="29"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q32" s="29"/>
+      <c r="R32" s="28"/>
+    </row>
+    <row r="33" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B33" s="5">
         <v>29</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="6" t="s">
         <v>32</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E33" s="28"/>
-      <c r="F33" s="29"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="28"/>
       <c r="N33" s="5">
         <v>29</v>
       </c>
@@ -2394,21 +7485,21 @@
       <c r="P33" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="32"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q33" s="27"/>
+      <c r="R33" s="31"/>
+    </row>
+    <row r="34" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B34" s="5">
         <v>30</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="6" t="s">
         <v>33</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E34" s="31"/>
-      <c r="F34" s="18"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="17"/>
       <c r="N34" s="5">
         <v>30</v>
       </c>
@@ -2418,21 +7509,21 @@
       <c r="P34" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="Q34" s="52"/>
-      <c r="R34" s="32"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q34" s="40"/>
+      <c r="R34" s="31"/>
+    </row>
+    <row r="35" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B35" s="5">
         <v>31</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E35" s="17"/>
-      <c r="F35" s="32"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="31"/>
       <c r="N35" s="5">
         <v>31</v>
       </c>
@@ -2442,21 +7533,21 @@
       <c r="P35" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="29"/>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q35" s="40"/>
+      <c r="R35" s="28"/>
+    </row>
+    <row r="36" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B36" s="5">
         <v>32</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E36" s="27"/>
-      <c r="F36" s="18"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="17"/>
       <c r="N36" s="5">
         <v>32</v>
       </c>
@@ -2466,21 +7557,21 @@
       <c r="P36" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="18"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="Q36" s="30"/>
+      <c r="R36" s="17"/>
+    </row>
+    <row r="37" spans="2:18" ht="14.25" x14ac:dyDescent="0.2">
       <c r="B37" s="5">
         <v>33</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="27"/>
-      <c r="F37" s="23"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="22"/>
       <c r="N37" s="5">
         <v>33</v>
       </c>
@@ -2490,32 +7581,32 @@
       <c r="P37" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="Q37" s="59"/>
-      <c r="R37" s="58"/>
-    </row>
-    <row r="38" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="9">
+      <c r="Q37" s="47"/>
+      <c r="R37" s="46"/>
+    </row>
+    <row r="38" spans="2:18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="8">
         <v>34</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E38" s="33"/>
-      <c r="F38" s="34"/>
-      <c r="N38" s="9">
+      <c r="E38" s="32"/>
+      <c r="F38" s="33"/>
+      <c r="N38" s="8">
         <v>34</v>
       </c>
-      <c r="O38" s="47" t="s">
+      <c r="O38" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="P38" s="11" t="s">
+      <c r="P38" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="Q38" s="60"/>
-      <c r="R38" s="11"/>
+      <c r="Q38" s="48"/>
+      <c r="R38" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="7">
